--- a/files/九龙-何文田-瑜一．天海.xlsx
+++ b/files/九龙-何文田-瑜一．天海.xlsx
@@ -130,6 +130,11 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00000000"/>
       <sz val="8"/>
@@ -137,11 +142,6 @@
     <font>
       <name val="Microsoft YaHei"/>
       <color rgb="00002060"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
       <sz val="8"/>
     </font>
   </fonts>
@@ -289,13 +289,13 @@
     <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -932,7 +932,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2023-07-24</t>
+          <t>2023-07-25</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -1870,7 +1870,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
@@ -1994,7 +1994,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -2118,7 +2118,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
@@ -2242,7 +2242,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2024-04-11</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -2428,7 +2428,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -2552,7 +2552,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2023-06-13</t>
+          <t>2023-06-14</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2614,7 +2614,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -2738,7 +2738,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
+          <t>2023-08-02</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
@@ -2924,7 +2924,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -2986,7 +2986,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -3118,7 +3118,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="H44" s="5" t="n">
@@ -3428,7 +3428,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
@@ -3490,7 +3490,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="H46" s="5" t="n">
@@ -3552,7 +3552,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -3614,7 +3614,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="H48" s="5" t="n">
@@ -3676,7 +3676,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -3738,7 +3738,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -3800,7 +3800,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -3924,7 +3924,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="H54" s="5" t="n">
@@ -4048,7 +4048,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="H56" s="5" t="n">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="H57" s="5" t="n">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="H58" s="5" t="n">
@@ -4296,7 +4296,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -4358,7 +4358,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="H60" s="5" t="n">
@@ -4420,7 +4420,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -4544,7 +4544,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -4606,7 +4606,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="H64" s="5" t="n">
@@ -4668,7 +4668,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
@@ -4730,7 +4730,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>2026-01-11</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="H66" s="5" t="n">
@@ -4862,7 +4862,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="H68" s="5" t="n">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="H69" s="5" t="n">
@@ -4986,7 +4986,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="H70" s="5" t="n">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
@@ -5180,7 +5180,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
@@ -5242,7 +5242,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
@@ -5374,7 +5374,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="H76" s="5" t="n">
@@ -5436,7 +5436,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="H77" s="5" t="n">
@@ -5498,7 +5498,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="H78" s="5" t="n">
@@ -5630,7 +5630,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="H80" s="5" t="n">
@@ -5762,7 +5762,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="H82" s="5" t="n">
@@ -5894,7 +5894,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="H84" s="5" t="n">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="H85" s="5" t="n">
@@ -6018,7 +6018,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="H86" s="5" t="n">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="H88" s="5" t="n">
@@ -6422,7 +6422,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H92" s="5" t="n">
@@ -6484,7 +6484,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H93" s="5" t="n">
@@ -6616,7 +6616,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>2023-07-04</t>
+          <t>2023-07-05</t>
         </is>
       </c>
       <c r="H95" s="5" t="n">
@@ -6678,7 +6678,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="H96" s="5" t="n">
@@ -6740,7 +6740,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="H97" s="5" t="n">
@@ -6867,7 +6867,7 @@
       </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G99" s="3" t="inlineStr">
@@ -6877,12 +6877,12 @@
       </c>
       <c r="H99" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I99" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J99" s="3" t="inlineStr">
@@ -6892,12 +6892,12 @@
       </c>
       <c r="K99" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L99" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M99" s="3" t="inlineStr">
@@ -6907,7 +6907,7 @@
       </c>
       <c r="N99" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -6937,7 +6937,7 @@
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G100" s="3" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="H100" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I100" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J100" s="3" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="K100" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L100" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M100" s="3" t="inlineStr">
@@ -6977,7 +6977,7 @@
       </c>
       <c r="N100" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -7007,7 +7007,7 @@
       </c>
       <c r="F101" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G101" s="3" t="inlineStr">
@@ -7017,12 +7017,12 @@
       </c>
       <c r="H101" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I101" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J101" s="3" t="inlineStr">
@@ -7032,12 +7032,12 @@
       </c>
       <c r="K101" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L101" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M101" s="3" t="inlineStr">
@@ -7047,7 +7047,7 @@
       </c>
       <c r="N101" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -7082,7 +7082,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>2023-12-20</t>
+          <t>2023-12-21</t>
         </is>
       </c>
       <c r="H102" s="5" t="n">
@@ -7144,7 +7144,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="H103" s="5" t="n">
@@ -7206,7 +7206,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="H104" s="5" t="n">
@@ -7268,7 +7268,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="H105" s="5" t="n">
@@ -7400,7 +7400,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>2023-06-12</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="H107" s="5" t="n">
@@ -7462,7 +7462,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
+          <t>2025-04-25</t>
         </is>
       </c>
       <c r="H108" s="5" t="n">
@@ -7524,7 +7524,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="H109" s="5" t="n">
@@ -7586,7 +7586,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-04-30</t>
         </is>
       </c>
       <c r="H110" s="5" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="H111" s="5" t="n">
@@ -7710,7 +7710,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-05-23</t>
         </is>
       </c>
       <c r="H112" s="5" t="n">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="H113" s="5" t="n">
@@ -7834,7 +7834,7 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="H114" s="5" t="n">
@@ -7896,7 +7896,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-04-30</t>
         </is>
       </c>
       <c r="H115" s="5" t="n">
@@ -7958,7 +7958,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>2024-03-25</t>
+          <t>2024-03-26</t>
         </is>
       </c>
       <c r="H116" s="5" t="n">
@@ -8020,7 +8020,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="H117" s="5" t="n">
@@ -8082,7 +8082,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="H118" s="5" t="n">
@@ -8144,7 +8144,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>2025-05-05</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="H119" s="5" t="n">
@@ -8206,7 +8206,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
+          <t>2025-04-25</t>
         </is>
       </c>
       <c r="H120" s="5" t="n">
@@ -8268,7 +8268,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="H121" s="5" t="n">
@@ -8330,7 +8330,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>2023-12-18</t>
+          <t>2023-12-19</t>
         </is>
       </c>
       <c r="H122" s="5" t="n">
@@ -8392,7 +8392,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="H123" s="5" t="n">
@@ -8454,7 +8454,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="H124" s="5" t="n">
@@ -8516,7 +8516,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
+          <t>2025-04-25</t>
         </is>
       </c>
       <c r="H125" s="5" t="n">
@@ -8578,7 +8578,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="H126" s="5" t="n">
@@ -8640,7 +8640,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>2023-06-08</t>
+          <t>2023-06-09</t>
         </is>
       </c>
       <c r="H127" s="5" t="n">
@@ -8702,7 +8702,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="H128" s="5" t="n">
@@ -8764,7 +8764,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
+          <t>2025-04-25</t>
         </is>
       </c>
       <c r="H129" s="5" t="n">
@@ -8826,7 +8826,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="H130" s="5" t="n">
@@ -8888,7 +8888,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
+          <t>2024-05-08</t>
         </is>
       </c>
       <c r="H131" s="5" t="n">
@@ -8950,7 +8950,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>2023-06-12</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="H132" s="5" t="n">
@@ -9012,7 +9012,7 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="H133" s="5" t="n">
@@ -9074,7 +9074,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="H134" s="5" t="n">
@@ -9136,7 +9136,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-04-30</t>
         </is>
       </c>
       <c r="H135" s="5" t="n">
@@ -9198,7 +9198,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-04-30</t>
         </is>
       </c>
       <c r="H136" s="5" t="n">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>2023-06-13</t>
+          <t>2023-06-14</t>
         </is>
       </c>
       <c r="H137" s="5" t="n">
@@ -9322,7 +9322,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
+          <t>2025-04-25</t>
         </is>
       </c>
       <c r="H138" s="5" t="n">
@@ -9384,7 +9384,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="H139" s="5" t="n">
@@ -9446,7 +9446,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="H140" s="5" t="n">
@@ -9508,7 +9508,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>2025-05-18</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="H141" s="5" t="n">
@@ -9570,7 +9570,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>2023-06-14</t>
+          <t>2023-06-15</t>
         </is>
       </c>
       <c r="H142" s="5" t="n">
@@ -9632,7 +9632,7 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-04-30</t>
         </is>
       </c>
       <c r="H143" s="5" t="n">
@@ -9694,7 +9694,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-04-30</t>
         </is>
       </c>
       <c r="H144" s="5" t="n">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>2024-07-15</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="H145" s="5" t="n">
@@ -9818,7 +9818,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="H146" s="5" t="n">
@@ -9880,7 +9880,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>2023-06-13</t>
+          <t>2023-06-14</t>
         </is>
       </c>
       <c r="H147" s="5" t="n">
@@ -9942,7 +9942,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
+          <t>2025-04-25</t>
         </is>
       </c>
       <c r="H148" s="5" t="n">
@@ -10004,7 +10004,7 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="H149" s="5" t="n">
@@ -10066,7 +10066,7 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>2024-07-10</t>
+          <t>2024-07-11</t>
         </is>
       </c>
       <c r="H150" s="5" t="n">
@@ -10123,30 +10123,38 @@
       </c>
       <c r="F151" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="H151" s="5" t="n">
-        <v>27068000</v>
-      </c>
-      <c r="I151" s="5" t="n">
-        <v>28196</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H151" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I151" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J151" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K151" s="5" t="n">
-        <v>27068000</v>
-      </c>
-      <c r="L151" s="5" t="n">
-        <v>28196</v>
+      <c r="K151" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L151" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M151" s="3" t="inlineStr">
         <is>
@@ -10155,7 +10163,7 @@
       </c>
       <c r="N151" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -10190,7 +10198,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>2023-06-18</t>
+          <t>2023-06-19</t>
         </is>
       </c>
       <c r="H152" s="5" t="n">
@@ -10252,7 +10260,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="H153" s="5" t="n">
@@ -10314,7 +10322,7 @@
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="H154" s="5" t="n">
@@ -10376,7 +10384,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>2024-11-20</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="H155" s="5" t="n">
@@ -10438,7 +10446,7 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="H156" s="5" t="n">
@@ -10500,7 +10508,7 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>2023-07-11</t>
+          <t>2023-07-12</t>
         </is>
       </c>
       <c r="H157" s="5" t="n">
@@ -10562,7 +10570,7 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="H158" s="5" t="n">
@@ -10624,7 +10632,7 @@
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-04-30</t>
         </is>
       </c>
       <c r="H159" s="5" t="n">
@@ -10686,7 +10694,7 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="H160" s="5" t="n">
@@ -10748,7 +10756,7 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>2023-08-08</t>
+          <t>2023-08-09</t>
         </is>
       </c>
       <c r="H161" s="5" t="n">
@@ -10810,7 +10818,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>2023-06-13</t>
+          <t>2023-06-14</t>
         </is>
       </c>
       <c r="H162" s="5" t="n">
@@ -10872,7 +10880,7 @@
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-04-30</t>
         </is>
       </c>
       <c r="H163" s="5" t="n">
@@ -10934,7 +10942,7 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="H164" s="5" t="n">
@@ -10996,7 +11004,7 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="H165" s="5" t="n">
@@ -11058,7 +11066,7 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>2025-05-05</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="H166" s="5" t="n">
@@ -11120,7 +11128,7 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2024-04-09</t>
         </is>
       </c>
       <c r="H167" s="5" t="n">
@@ -11182,7 +11190,7 @@
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-04-30</t>
         </is>
       </c>
       <c r="H168" s="5" t="n">
@@ -11244,7 +11252,7 @@
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="H169" s="5" t="n">
@@ -11306,7 +11314,7 @@
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-04-30</t>
         </is>
       </c>
       <c r="H170" s="5" t="n">
@@ -11368,7 +11376,7 @@
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>2025-05-05</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="H171" s="5" t="n">
@@ -11430,7 +11438,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>2023-07-17</t>
+          <t>2023-07-18</t>
         </is>
       </c>
       <c r="H172" s="5" t="n">
@@ -11492,7 +11500,7 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="H173" s="5" t="n">
@@ -11554,7 +11562,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="H174" s="5" t="n">
@@ -11616,7 +11624,7 @@
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="H175" s="5" t="n">
@@ -11678,7 +11686,7 @@
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="H176" s="5" t="n">
@@ -11740,7 +11748,7 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>2023-06-13</t>
+          <t>2023-06-14</t>
         </is>
       </c>
       <c r="H177" s="5" t="n">
@@ -11802,7 +11810,7 @@
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="H178" s="5" t="n">
@@ -11864,7 +11872,7 @@
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
+          <t>2025-04-25</t>
         </is>
       </c>
       <c r="H179" s="5" t="n">
@@ -11926,7 +11934,7 @@
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="H180" s="5" t="n">
@@ -11988,7 +11996,7 @@
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="H181" s="5" t="n">
@@ -12050,7 +12058,7 @@
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>2023-06-13</t>
+          <t>2023-06-14</t>
         </is>
       </c>
       <c r="H182" s="5" t="n">
@@ -12112,7 +12120,7 @@
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="H183" s="5" t="n">
@@ -12174,7 +12182,7 @@
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="H184" s="5" t="n">
@@ -12236,7 +12244,7 @@
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
+          <t>2025-04-25</t>
         </is>
       </c>
       <c r="H185" s="5" t="n">
@@ -12298,7 +12306,7 @@
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>2023-06-13</t>
+          <t>2023-06-14</t>
         </is>
       </c>
       <c r="H186" s="5" t="n">
@@ -12360,7 +12368,7 @@
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="H187" s="5" t="n">
@@ -12422,7 +12430,7 @@
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
+          <t>2025-04-25</t>
         </is>
       </c>
       <c r="H188" s="5" t="n">
@@ -12484,7 +12492,7 @@
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="H189" s="5" t="n">
@@ -12546,7 +12554,7 @@
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>2025-05-05</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="H190" s="5" t="n">
@@ -12608,7 +12616,7 @@
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>2023-06-12</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="H191" s="5" t="n">
@@ -12670,7 +12678,7 @@
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>2023-06-11</t>
+          <t>2023-06-12</t>
         </is>
       </c>
       <c r="H192" s="5" t="n">
@@ -12732,7 +12740,7 @@
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="H193" s="5" t="n">
@@ -12794,7 +12802,7 @@
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>2024-11-25</t>
+          <t>2024-11-26</t>
         </is>
       </c>
       <c r="H194" s="5" t="n">
@@ -12856,7 +12864,7 @@
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>2024-07-15</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="H195" s="5" t="n">
@@ -12918,7 +12926,7 @@
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="H196" s="5" t="n">
@@ -12980,7 +12988,7 @@
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>2023-06-14</t>
+          <t>2023-06-15</t>
         </is>
       </c>
       <c r="H197" s="5" t="n">
@@ -13042,7 +13050,7 @@
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="H198" s="5" t="n">
@@ -13104,7 +13112,7 @@
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="H199" s="5" t="n">
@@ -13166,7 +13174,7 @@
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>2024-11-24</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="H200" s="5" t="n">
@@ -13228,7 +13236,7 @@
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="H201" s="5" t="n">
@@ -13290,7 +13298,7 @@
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="H202" s="5" t="n">
@@ -13352,7 +13360,7 @@
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-04-30</t>
         </is>
       </c>
       <c r="H203" s="5" t="n">
@@ -13414,7 +13422,7 @@
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="H204" s="5" t="n">
@@ -13476,7 +13484,7 @@
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2024-07-10</t>
         </is>
       </c>
       <c r="H205" s="5" t="n">
@@ -13538,7 +13546,7 @@
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="H206" s="5" t="n">
@@ -13600,7 +13608,7 @@
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="H207" s="5" t="n">
@@ -13662,7 +13670,7 @@
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="H208" s="5" t="n">
@@ -13724,7 +13732,7 @@
       </c>
       <c r="G209" s="3" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-04-30</t>
         </is>
       </c>
       <c r="H209" s="5" t="n">
@@ -13786,7 +13794,7 @@
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="H210" s="5" t="n">
@@ -13848,7 +13856,7 @@
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="H211" s="5" t="n">
@@ -13910,7 +13918,7 @@
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="H212" s="5" t="n">
@@ -13972,7 +13980,7 @@
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-04-30</t>
         </is>
       </c>
       <c r="H213" s="5" t="n">
@@ -14034,7 +14042,7 @@
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="H214" s="5" t="n">
@@ -14096,7 +14104,7 @@
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="H215" s="5" t="n">
@@ -14158,7 +14166,7 @@
       </c>
       <c r="G216" s="3" t="inlineStr">
         <is>
-          <t>2024-04-25</t>
+          <t>2024-04-26</t>
         </is>
       </c>
       <c r="H216" s="5" t="n">
@@ -14220,7 +14228,7 @@
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>2024-03-11</t>
+          <t>2024-03-12</t>
         </is>
       </c>
       <c r="H217" s="5" t="n">
@@ -14282,7 +14290,7 @@
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
+          <t>2025-04-25</t>
         </is>
       </c>
       <c r="H218" s="5" t="n">
@@ -14344,7 +14352,7 @@
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="H219" s="5" t="n">
@@ -14406,7 +14414,7 @@
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="H220" s="5" t="n">
@@ -14468,7 +14476,7 @@
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t>2025-07-13</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="H221" s="5" t="n">
@@ -14530,7 +14538,7 @@
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
+          <t>2023-06-21</t>
         </is>
       </c>
       <c r="H222" s="5" t="n">
@@ -14592,7 +14600,7 @@
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-04-30</t>
         </is>
       </c>
       <c r="H223" s="5" t="n">
@@ -14654,7 +14662,7 @@
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="H224" s="5" t="n">
@@ -14716,7 +14724,7 @@
       </c>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2024-07-31</t>
         </is>
       </c>
       <c r="H225" s="5" t="n">
@@ -14778,7 +14786,7 @@
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="H226" s="5" t="n">
@@ -14835,7 +14843,7 @@
       </c>
       <c r="F227" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G227" s="3" t="inlineStr">
@@ -14905,7 +14913,7 @@
       </c>
       <c r="F228" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G228" s="3" t="inlineStr">
@@ -14975,7 +14983,7 @@
       </c>
       <c r="F229" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G229" s="3" t="inlineStr">
@@ -15045,7 +15053,7 @@
       </c>
       <c r="F230" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G230" s="3" t="inlineStr">
@@ -15260,7 +15268,7 @@
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="H233" s="5" t="n">
@@ -15322,7 +15330,7 @@
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="H234" s="5" t="n">
@@ -15524,7 +15532,7 @@
       </c>
       <c r="G237" s="3" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="H237" s="5" t="n">
@@ -15796,7 +15804,7 @@
       </c>
       <c r="G241" s="3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="H241" s="5" t="n">
@@ -16060,7 +16068,7 @@
       </c>
       <c r="G245" s="3" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="H245" s="5" t="n">
@@ -16332,7 +16340,7 @@
       </c>
       <c r="G249" s="3" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="H249" s="5" t="n">
@@ -16394,7 +16402,7 @@
       </c>
       <c r="G250" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H250" s="5" t="n">
@@ -16596,7 +16604,7 @@
       </c>
       <c r="G253" s="3" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="H253" s="5" t="n">
@@ -16798,7 +16806,7 @@
       </c>
       <c r="G256" s="3" t="inlineStr">
         <is>
-          <t>2023-12-06</t>
+          <t>2023-12-07</t>
         </is>
       </c>
       <c r="H256" s="5" t="n">
@@ -16860,7 +16868,7 @@
       </c>
       <c r="G257" s="3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H257" s="5" t="n">
@@ -17132,7 +17140,7 @@
       </c>
       <c r="G261" s="3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="H261" s="5" t="n">
@@ -17404,7 +17412,7 @@
       </c>
       <c r="G265" s="3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H265" s="5" t="n">
@@ -17668,7 +17676,7 @@
       </c>
       <c r="G269" s="3" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="H269" s="5" t="n">
@@ -17730,7 +17738,7 @@
       </c>
       <c r="G270" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H270" s="5" t="n">
@@ -17924,7 +17932,7 @@
       </c>
       <c r="G273" s="3" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="H273" s="5" t="n">
@@ -17986,7 +17994,7 @@
       </c>
       <c r="G274" s="3" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="H274" s="5" t="n">
@@ -18188,7 +18196,7 @@
       </c>
       <c r="G277" s="3" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-04-11</t>
         </is>
       </c>
       <c r="H277" s="5" t="n">
@@ -18250,7 +18258,7 @@
       </c>
       <c r="G278" s="3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="H278" s="5" t="n">
@@ -18452,7 +18460,7 @@
       </c>
       <c r="G281" s="3" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="H281" s="5" t="n">
@@ -18514,7 +18522,7 @@
       </c>
       <c r="G282" s="3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="H282" s="5" t="n">
@@ -18646,7 +18654,7 @@
       </c>
       <c r="G284" s="3" t="inlineStr">
         <is>
-          <t>2023-06-11</t>
+          <t>2023-06-12</t>
         </is>
       </c>
       <c r="H284" s="5" t="n">
@@ -18708,7 +18716,7 @@
       </c>
       <c r="G285" s="3" t="inlineStr">
         <is>
-          <t>2023-06-11</t>
+          <t>2023-06-12</t>
         </is>
       </c>
       <c r="H285" s="5" t="n">
@@ -18770,7 +18778,7 @@
       </c>
       <c r="G286" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="H286" s="5" t="n">
@@ -18902,7 +18910,7 @@
       </c>
       <c r="G288" s="3" t="inlineStr">
         <is>
-          <t>2023-07-03</t>
+          <t>2023-07-04</t>
         </is>
       </c>
       <c r="H288" s="5" t="n">
@@ -18964,7 +18972,7 @@
       </c>
       <c r="G289" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="H289" s="5" t="n">
@@ -19026,7 +19034,7 @@
       </c>
       <c r="G290" s="3" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="H290" s="5" t="n">
@@ -19158,7 +19166,7 @@
       </c>
       <c r="G292" s="3" t="inlineStr">
         <is>
-          <t>2023-11-12</t>
+          <t>2023-11-13</t>
         </is>
       </c>
       <c r="H292" s="5" t="n">
@@ -19290,7 +19298,7 @@
       </c>
       <c r="G294" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="H294" s="5" t="n">
@@ -19422,7 +19430,7 @@
       </c>
       <c r="G296" s="3" t="inlineStr">
         <is>
-          <t>2024-02-06</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="H296" s="5" t="n">
@@ -19484,7 +19492,7 @@
       </c>
       <c r="G297" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H297" s="5" t="n">
@@ -19756,7 +19764,7 @@
       </c>
       <c r="G301" s="3" t="inlineStr">
         <is>
-          <t>2023-06-26</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="H301" s="5" t="n">
@@ -19958,7 +19966,7 @@
       </c>
       <c r="G304" s="3" t="inlineStr">
         <is>
-          <t>2023-06-14</t>
+          <t>2023-06-15</t>
         </is>
       </c>
       <c r="H304" s="5" t="n">
@@ -20020,7 +20028,7 @@
       </c>
       <c r="G305" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H305" s="5" t="n">
@@ -20292,7 +20300,7 @@
       </c>
       <c r="G309" s="3" t="inlineStr">
         <is>
-          <t>2023-06-13</t>
+          <t>2023-06-14</t>
         </is>
       </c>
       <c r="H309" s="5" t="n">
@@ -20494,7 +20502,7 @@
       </c>
       <c r="G312" s="3" t="inlineStr">
         <is>
-          <t>2023-06-12</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="H312" s="5" t="n">
@@ -20556,7 +20564,7 @@
       </c>
       <c r="G313" s="3" t="inlineStr">
         <is>
-          <t>2024-03-21</t>
+          <t>2024-03-22</t>
         </is>
       </c>
       <c r="H313" s="5" t="n">
@@ -20758,7 +20766,7 @@
       </c>
       <c r="G316" s="3" t="inlineStr">
         <is>
-          <t>2023-06-12</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="H316" s="5" t="n">
@@ -20820,7 +20828,7 @@
       </c>
       <c r="G317" s="3" t="inlineStr">
         <is>
-          <t>2023-07-03</t>
+          <t>2023-07-04</t>
         </is>
       </c>
       <c r="H317" s="5" t="n">
@@ -20952,7 +20960,7 @@
       </c>
       <c r="G319" s="3" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="H319" s="5" t="n">
@@ -21009,7 +21017,7 @@
       </c>
       <c r="F320" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G320" s="3" t="inlineStr">
@@ -21017,31 +21025,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H320" s="5" t="n">
-        <v>19574000</v>
-      </c>
-      <c r="I320" s="5" t="n">
-        <v>35589</v>
+      <c r="H320" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I320" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J320" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
-        </is>
-      </c>
-      <c r="K320" s="5" t="n">
-        <v>16637900</v>
-      </c>
-      <c r="L320" s="5" t="n">
-        <v>30251</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K320" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L320" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M320" s="3" t="inlineStr">
         <is>
-          <t>如「瑜」得水 120天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N320" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -21071,7 +21087,7 @@
       </c>
       <c r="F321" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G321" s="3" t="inlineStr">
@@ -21079,31 +21095,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H321" s="5" t="n">
-        <v>19882000</v>
-      </c>
-      <c r="I321" s="5" t="n">
-        <v>35823</v>
+      <c r="H321" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I321" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J321" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
-        </is>
-      </c>
-      <c r="K321" s="5" t="n">
-        <v>16899700</v>
-      </c>
-      <c r="L321" s="5" t="n">
-        <v>30450</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K321" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L321" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M321" s="3" t="inlineStr">
         <is>
-          <t>如「瑜」得水 120天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N321" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -21208,7 +21232,7 @@
       </c>
       <c r="G323" s="3" t="inlineStr">
         <is>
-          <t>2023-11-13</t>
+          <t>2023-11-14</t>
         </is>
       </c>
       <c r="H323" s="5" t="n">
@@ -21265,7 +21289,7 @@
       </c>
       <c r="F324" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G324" s="3" t="inlineStr">
@@ -21275,12 +21299,12 @@
       </c>
       <c r="H324" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I324" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J324" s="3" t="inlineStr">
@@ -21290,12 +21314,12 @@
       </c>
       <c r="K324" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L324" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M324" s="3" t="inlineStr">
@@ -21305,7 +21329,7 @@
       </c>
       <c r="N324" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -21340,7 +21364,7 @@
       </c>
       <c r="G325" s="3" t="inlineStr">
         <is>
-          <t>2026-01-11</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="H325" s="5" t="n">
@@ -21472,7 +21496,7 @@
       </c>
       <c r="G327" s="3" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="H327" s="5" t="n">
@@ -21534,7 +21558,7 @@
       </c>
       <c r="G328" s="3" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="H328" s="5" t="n">
@@ -21596,7 +21620,7 @@
       </c>
       <c r="G329" s="3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="H329" s="5" t="n">
@@ -21658,7 +21682,7 @@
       </c>
       <c r="G330" s="3" t="inlineStr">
         <is>
-          <t>2023-11-02</t>
+          <t>2023-11-03</t>
         </is>
       </c>
       <c r="H330" s="5" t="n">
@@ -21720,7 +21744,7 @@
       </c>
       <c r="G331" s="3" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="H331" s="5" t="n">
@@ -21782,7 +21806,7 @@
       </c>
       <c r="G332" s="3" t="inlineStr">
         <is>
-          <t>2025-06-05</t>
+          <t>2025-06-06</t>
         </is>
       </c>
       <c r="H332" s="5" t="n">
@@ -21844,7 +21868,7 @@
       </c>
       <c r="G333" s="3" t="inlineStr">
         <is>
-          <t>2025-05-12</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="H333" s="5" t="n">
@@ -21976,7 +22000,7 @@
       </c>
       <c r="G335" s="3" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-05-23</t>
         </is>
       </c>
       <c r="H335" s="5" t="n">
@@ -22038,7 +22062,7 @@
       </c>
       <c r="G336" s="3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="H336" s="5" t="n">
@@ -22100,7 +22124,7 @@
       </c>
       <c r="G337" s="3" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="H337" s="5" t="n">
@@ -22162,7 +22186,7 @@
       </c>
       <c r="G338" s="3" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="H338" s="5" t="n">
@@ -22294,7 +22318,7 @@
       </c>
       <c r="G340" s="3" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="H340" s="5" t="n">
@@ -22356,7 +22380,7 @@
       </c>
       <c r="G341" s="3" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="H341" s="5" t="n">
@@ -22418,7 +22442,7 @@
       </c>
       <c r="G342" s="3" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="H342" s="5" t="n">
@@ -22480,7 +22504,7 @@
       </c>
       <c r="G343" s="3" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="H343" s="5" t="n">
@@ -22542,7 +22566,7 @@
       </c>
       <c r="G344" s="3" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="H344" s="5" t="n">
@@ -22604,7 +22628,7 @@
       </c>
       <c r="G345" s="3" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="H345" s="5" t="n">
@@ -22666,7 +22690,7 @@
       </c>
       <c r="G346" s="3" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="H346" s="5" t="n">
@@ -22728,7 +22752,7 @@
       </c>
       <c r="G347" s="3" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="H347" s="5" t="n">
@@ -22790,7 +22814,7 @@
       </c>
       <c r="G348" s="3" t="inlineStr">
         <is>
-          <t>2025-05-18</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="H348" s="5" t="n">
@@ -22922,7 +22946,7 @@
       </c>
       <c r="G350" s="3" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="H350" s="5" t="n">
@@ -22984,7 +23008,7 @@
       </c>
       <c r="G351" s="3" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="H351" s="5" t="n">
@@ -23046,7 +23070,7 @@
       </c>
       <c r="G352" s="3" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="H352" s="5" t="n">
@@ -23108,7 +23132,7 @@
       </c>
       <c r="G353" s="3" t="inlineStr">
         <is>
-          <t>2025-05-11</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="H353" s="5" t="n">
@@ -23170,7 +23194,7 @@
       </c>
       <c r="G354" s="3" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="H354" s="5" t="n">
@@ -23232,7 +23256,7 @@
       </c>
       <c r="G355" s="3" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="H355" s="5" t="n">
@@ -23294,7 +23318,7 @@
       </c>
       <c r="G356" s="3" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="H356" s="5" t="n">
@@ -23356,7 +23380,7 @@
       </c>
       <c r="G357" s="3" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="H357" s="5" t="n">
@@ -23418,7 +23442,7 @@
       </c>
       <c r="G358" s="3" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="H358" s="5" t="n">
@@ -23480,7 +23504,7 @@
       </c>
       <c r="G359" s="3" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="H359" s="5" t="n">
@@ -23542,7 +23566,7 @@
       </c>
       <c r="G360" s="3" t="inlineStr">
         <is>
-          <t>2023-06-11</t>
+          <t>2023-06-12</t>
         </is>
       </c>
       <c r="H360" s="5" t="n">
@@ -23604,7 +23628,7 @@
       </c>
       <c r="G361" s="3" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="H361" s="5" t="n">
@@ -23666,7 +23690,7 @@
       </c>
       <c r="G362" s="3" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="H362" s="5" t="n">
@@ -23728,7 +23752,7 @@
       </c>
       <c r="G363" s="3" t="inlineStr">
         <is>
-          <t>2023-12-07</t>
+          <t>2023-12-08</t>
         </is>
       </c>
       <c r="H363" s="5" t="n">
@@ -23790,7 +23814,7 @@
       </c>
       <c r="G364" s="3" t="inlineStr">
         <is>
-          <t>2023-06-14</t>
+          <t>2023-06-15</t>
         </is>
       </c>
       <c r="H364" s="5" t="n">
@@ -23852,7 +23876,7 @@
       </c>
       <c r="G365" s="3" t="inlineStr">
         <is>
-          <t>2025-06-05</t>
+          <t>2025-06-06</t>
         </is>
       </c>
       <c r="H365" s="5" t="n">
@@ -23914,7 +23938,7 @@
       </c>
       <c r="G366" s="3" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="H366" s="5" t="n">
@@ -23976,7 +24000,7 @@
       </c>
       <c r="G367" s="3" t="inlineStr">
         <is>
-          <t>2025-05-12</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="H367" s="5" t="n">
@@ -24038,7 +24062,7 @@
       </c>
       <c r="G368" s="3" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="H368" s="5" t="n">
@@ -24100,7 +24124,7 @@
       </c>
       <c r="G369" s="3" t="inlineStr">
         <is>
-          <t>2023-06-29</t>
+          <t>2023-06-30</t>
         </is>
       </c>
       <c r="H369" s="5" t="n">
@@ -24162,7 +24186,7 @@
       </c>
       <c r="G370" s="3" t="inlineStr">
         <is>
-          <t>2023-06-19</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="H370" s="5" t="n">
@@ -24224,7 +24248,7 @@
       </c>
       <c r="G371" s="3" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="H371" s="5" t="n">
@@ -24286,7 +24310,7 @@
       </c>
       <c r="G372" s="3" t="inlineStr">
         <is>
-          <t>2023-09-24</t>
+          <t>2023-09-25</t>
         </is>
       </c>
       <c r="H372" s="5" t="n">
@@ -24348,7 +24372,7 @@
       </c>
       <c r="G373" s="3" t="inlineStr">
         <is>
-          <t>2025-05-12</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="H373" s="5" t="n">
@@ -24410,7 +24434,7 @@
       </c>
       <c r="G374" s="3" t="inlineStr">
         <is>
-          <t>2023-07-24</t>
+          <t>2023-07-25</t>
         </is>
       </c>
       <c r="H374" s="5" t="n">
@@ -24472,7 +24496,7 @@
       </c>
       <c r="G375" s="3" t="inlineStr">
         <is>
-          <t>2023-06-08</t>
+          <t>2023-06-09</t>
         </is>
       </c>
       <c r="H375" s="5" t="n">
@@ -24534,7 +24558,7 @@
       </c>
       <c r="G376" s="3" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="H376" s="5" t="n">
@@ -24596,7 +24620,7 @@
       </c>
       <c r="G377" s="3" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="H377" s="5" t="n">
@@ -24658,7 +24682,7 @@
       </c>
       <c r="G378" s="3" t="inlineStr">
         <is>
-          <t>2025-05-11</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="H378" s="5" t="n">
@@ -24720,7 +24744,7 @@
       </c>
       <c r="G379" s="3" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="H379" s="5" t="n">
@@ -24782,7 +24806,7 @@
       </c>
       <c r="G380" s="3" t="inlineStr">
         <is>
-          <t>2023-06-12</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="H380" s="5" t="n">
@@ -24844,7 +24868,7 @@
       </c>
       <c r="G381" s="3" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="H381" s="5" t="n">
@@ -24906,7 +24930,7 @@
       </c>
       <c r="G382" s="3" t="inlineStr">
         <is>
-          <t>2025-05-05</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="H382" s="5" t="n">
@@ -24968,7 +24992,7 @@
       </c>
       <c r="G383" s="3" t="inlineStr">
         <is>
-          <t>2025-05-12</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="H383" s="5" t="n">
@@ -25030,7 +25054,7 @@
       </c>
       <c r="G384" s="3" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="H384" s="5" t="n">
@@ -25092,7 +25116,7 @@
       </c>
       <c r="G385" s="3" t="inlineStr">
         <is>
-          <t>2023-06-11</t>
+          <t>2023-06-12</t>
         </is>
       </c>
       <c r="H385" s="5" t="n">
@@ -25154,7 +25178,7 @@
       </c>
       <c r="G386" s="3" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="H386" s="5" t="n">
@@ -25216,7 +25240,7 @@
       </c>
       <c r="G387" s="3" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="H387" s="5" t="n">
@@ -25278,7 +25302,7 @@
       </c>
       <c r="G388" s="3" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="H388" s="5" t="n">
@@ -25340,7 +25364,7 @@
       </c>
       <c r="G389" s="3" t="inlineStr">
         <is>
-          <t>2023-10-08</t>
+          <t>2023-10-09</t>
         </is>
       </c>
       <c r="H389" s="5" t="n">
@@ -25402,7 +25426,7 @@
       </c>
       <c r="G390" s="3" t="inlineStr">
         <is>
-          <t>2023-06-18</t>
+          <t>2023-06-19</t>
         </is>
       </c>
       <c r="H390" s="5" t="n">
@@ -25464,7 +25488,7 @@
       </c>
       <c r="G391" s="3" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="H391" s="5" t="n">
@@ -25526,7 +25550,7 @@
       </c>
       <c r="G392" s="3" t="inlineStr">
         <is>
-          <t>2025-05-11</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="H392" s="5" t="n">
@@ -25588,7 +25612,7 @@
       </c>
       <c r="G393" s="3" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="H393" s="5" t="n">
@@ -25650,7 +25674,7 @@
       </c>
       <c r="G394" s="3" t="inlineStr">
         <is>
-          <t>2023-06-14</t>
+          <t>2023-06-15</t>
         </is>
       </c>
       <c r="H394" s="5" t="n">
@@ -25712,7 +25736,7 @@
       </c>
       <c r="G395" s="3" t="inlineStr">
         <is>
-          <t>2023-06-14</t>
+          <t>2023-06-15</t>
         </is>
       </c>
       <c r="H395" s="5" t="n">
@@ -25774,7 +25798,7 @@
       </c>
       <c r="G396" s="3" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="H396" s="5" t="n">
@@ -25836,7 +25860,7 @@
       </c>
       <c r="G397" s="3" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="H397" s="5" t="n">
@@ -25898,7 +25922,7 @@
       </c>
       <c r="G398" s="3" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="H398" s="5" t="n">
@@ -25960,7 +25984,7 @@
       </c>
       <c r="G399" s="3" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="H399" s="5" t="n">
@@ -26022,7 +26046,7 @@
       </c>
       <c r="G400" s="3" t="inlineStr">
         <is>
-          <t>2023-06-12</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="H400" s="5" t="n">
@@ -26084,7 +26108,7 @@
       </c>
       <c r="G401" s="3" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="H401" s="5" t="n">
@@ -26146,7 +26170,7 @@
       </c>
       <c r="G402" s="3" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="H402" s="5" t="n">
@@ -26208,7 +26232,7 @@
       </c>
       <c r="G403" s="3" t="inlineStr">
         <is>
-          <t>2023-06-12</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="H403" s="5" t="n">
@@ -26270,7 +26294,7 @@
       </c>
       <c r="G404" s="3" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="H404" s="5" t="n">
@@ -26332,7 +26356,7 @@
       </c>
       <c r="G405" s="3" t="inlineStr">
         <is>
-          <t>2023-06-11</t>
+          <t>2023-06-12</t>
         </is>
       </c>
       <c r="H405" s="5" t="n">
@@ -26394,7 +26418,7 @@
       </c>
       <c r="G406" s="3" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="H406" s="5" t="n">
@@ -26456,7 +26480,7 @@
       </c>
       <c r="G407" s="3" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="H407" s="5" t="n">
@@ -26518,7 +26542,7 @@
       </c>
       <c r="G408" s="3" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="H408" s="5" t="n">
@@ -26580,7 +26604,7 @@
       </c>
       <c r="G409" s="3" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="H409" s="5" t="n">
@@ -26642,7 +26666,7 @@
       </c>
       <c r="G410" s="3" t="inlineStr">
         <is>
-          <t>2023-06-11</t>
+          <t>2023-06-12</t>
         </is>
       </c>
       <c r="H410" s="5" t="n">
@@ -26704,7 +26728,7 @@
       </c>
       <c r="G411" s="3" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="H411" s="5" t="n">
@@ -26766,7 +26790,7 @@
       </c>
       <c r="G412" s="3" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="H412" s="5" t="n">
@@ -26828,7 +26852,7 @@
       </c>
       <c r="G413" s="3" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="H413" s="5" t="n">
@@ -26890,7 +26914,7 @@
       </c>
       <c r="G414" s="3" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="H414" s="5" t="n">
@@ -26952,7 +26976,7 @@
       </c>
       <c r="G415" s="3" t="inlineStr">
         <is>
-          <t>2023-06-14</t>
+          <t>2023-06-15</t>
         </is>
       </c>
       <c r="H415" s="5" t="n">
@@ -27014,7 +27038,7 @@
       </c>
       <c r="G416" s="3" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="H416" s="5" t="n">
@@ -27076,7 +27100,7 @@
       </c>
       <c r="G417" s="3" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="H417" s="5" t="n">
@@ -27138,7 +27162,7 @@
       </c>
       <c r="G418" s="3" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="H418" s="5" t="n">
@@ -27200,7 +27224,7 @@
       </c>
       <c r="G419" s="3" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="H419" s="5" t="n">
@@ -27262,7 +27286,7 @@
       </c>
       <c r="G420" s="3" t="inlineStr">
         <is>
-          <t>2023-06-13</t>
+          <t>2023-06-14</t>
         </is>
       </c>
       <c r="H420" s="5" t="n">
@@ -27324,7 +27348,7 @@
       </c>
       <c r="G421" s="3" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="H421" s="5" t="n">
@@ -27386,7 +27410,7 @@
       </c>
       <c r="G422" s="3" t="inlineStr">
         <is>
-          <t>2023-06-18</t>
+          <t>2023-06-19</t>
         </is>
       </c>
       <c r="H422" s="5" t="n">
@@ -27448,7 +27472,7 @@
       </c>
       <c r="G423" s="3" t="inlineStr">
         <is>
-          <t>2023-06-18</t>
+          <t>2023-06-19</t>
         </is>
       </c>
       <c r="H423" s="5" t="n">
@@ -27510,7 +27534,7 @@
       </c>
       <c r="G424" s="3" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="H424" s="5" t="n">
@@ -27572,7 +27596,7 @@
       </c>
       <c r="G425" s="3" t="inlineStr">
         <is>
-          <t>2023-06-12</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="H425" s="5" t="n">
@@ -27634,7 +27658,7 @@
       </c>
       <c r="G426" s="3" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="H426" s="5" t="n">
@@ -27696,7 +27720,7 @@
       </c>
       <c r="G427" s="3" t="inlineStr">
         <is>
-          <t>2023-06-13</t>
+          <t>2023-06-14</t>
         </is>
       </c>
       <c r="H427" s="5" t="n">
@@ -27758,7 +27782,7 @@
       </c>
       <c r="G428" s="3" t="inlineStr">
         <is>
-          <t>2023-06-12</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="H428" s="5" t="n">
@@ -27820,7 +27844,7 @@
       </c>
       <c r="G429" s="3" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="H429" s="5" t="n">
@@ -27882,7 +27906,7 @@
       </c>
       <c r="G430" s="3" t="inlineStr">
         <is>
-          <t>2023-06-13</t>
+          <t>2023-06-14</t>
         </is>
       </c>
       <c r="H430" s="5" t="n">
@@ -27944,7 +27968,7 @@
       </c>
       <c r="G431" s="3" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="H431" s="5" t="n">
@@ -28006,7 +28030,7 @@
       </c>
       <c r="G432" s="3" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="H432" s="5" t="n">
@@ -28068,7 +28092,7 @@
       </c>
       <c r="G433" s="3" t="inlineStr">
         <is>
-          <t>2023-06-19</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="H433" s="5" t="n">
@@ -28130,7 +28154,7 @@
       </c>
       <c r="G434" s="3" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="H434" s="5" t="n">
@@ -28192,7 +28216,7 @@
       </c>
       <c r="G435" s="3" t="inlineStr">
         <is>
-          <t>2023-06-11</t>
+          <t>2023-06-12</t>
         </is>
       </c>
       <c r="H435" s="5" t="n">
@@ -28254,7 +28278,7 @@
       </c>
       <c r="G436" s="3" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="H436" s="5" t="n">
@@ -28316,7 +28340,7 @@
       </c>
       <c r="G437" s="3" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="H437" s="5" t="n">
@@ -28378,7 +28402,7 @@
       </c>
       <c r="G438" s="3" t="inlineStr">
         <is>
-          <t>2025-05-11</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="H438" s="5" t="n">
@@ -28440,7 +28464,7 @@
       </c>
       <c r="G439" s="3" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="H439" s="5" t="n">
@@ -28502,7 +28526,7 @@
       </c>
       <c r="G440" s="3" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
+          <t>2023-06-28</t>
         </is>
       </c>
       <c r="H440" s="5" t="n">
@@ -28564,7 +28588,7 @@
       </c>
       <c r="G441" s="3" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H441" s="5" t="n">
@@ -28626,7 +28650,7 @@
       </c>
       <c r="G442" s="3" t="inlineStr">
         <is>
-          <t>2023-06-29</t>
+          <t>2023-06-30</t>
         </is>
       </c>
       <c r="H442" s="5" t="n">
@@ -28688,7 +28712,7 @@
       </c>
       <c r="G443" s="3" t="inlineStr">
         <is>
-          <t>2023-07-30</t>
+          <t>2023-07-31</t>
         </is>
       </c>
       <c r="H443" s="5" t="n">
@@ -28750,7 +28774,7 @@
       </c>
       <c r="G444" s="3" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="H444" s="5" t="n">
@@ -28812,7 +28836,7 @@
       </c>
       <c r="G445" s="3" t="inlineStr">
         <is>
-          <t>2023-06-11</t>
+          <t>2023-06-12</t>
         </is>
       </c>
       <c r="H445" s="5" t="n">
@@ -28874,7 +28898,7 @@
       </c>
       <c r="G446" s="3" t="inlineStr">
         <is>
-          <t>2026-01-04</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="H446" s="5" t="n">
@@ -28936,7 +28960,7 @@
       </c>
       <c r="G447" s="3" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="H447" s="5" t="n">
@@ -28998,7 +29022,7 @@
       </c>
       <c r="G448" s="3" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="H448" s="5" t="n">
@@ -29060,7 +29084,7 @@
       </c>
       <c r="G449" s="3" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="H449" s="5" t="n">
@@ -29166,7 +29190,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -29181,7 +29205,7 @@
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F3" s="18" t="inlineStr">
@@ -29279,7 +29303,7 @@
           <t>B | 1564呎 (4+房)
 $7273万
 $46,500/呎
-(26年-06月-17日)</t>
+(26年-06月-18日)</t>
         </is>
       </c>
       <c r="D6" s="21" t="inlineStr"/>
@@ -29299,7 +29323,7 @@
           <t>A | 968呎 (3房)
 $3533万
 $36,500/呎
-(26年-02月-10日)</t>
+(26年-02月-11日)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -29307,7 +29331,7 @@
           <t>B | 591呎 (2房)
 $2075万
 $35,105/呎
-(25年-05月-14日)</t>
+(25年-05月-15日)</t>
         </is>
       </c>
       <c r="D7" s="22" t="inlineStr">
@@ -29315,7 +29339,7 @@
           <t>C | 591呎 (2房)
 $2075万
 $35,105/呎
-(25年-05月-08日)</t>
+(25年-05月-09日)</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -29323,7 +29347,7 @@
           <t>D | 996呎 (3房)
 $4034万
 $40,500/呎
-(23年-07月-24日)</t>
+(23年-07月-25日)</t>
         </is>
       </c>
       <c r="F7" s="21" t="inlineStr"/>
@@ -29341,7 +29365,7 @@
           <t>A | 968呎 (3房)
 $3485万
 $36,000/呎
-(26年-01月-20日)</t>
+(26年-01月-21日)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -29349,7 +29373,7 @@
           <t>B | 591呎 (2房)
 $2130万
 $36,045/呎
-(25年-11月-10日)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr">
@@ -29357,7 +29381,7 @@
           <t>C | 591呎 (2房)
 $2066万
 $34,964/呎
-(25年-10月-27日)</t>
+(25年-10月-28日)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -29365,7 +29389,7 @@
           <t>D | 996呎 (3房)
 $3984万
 $40,000/呎
-(25年-07月-23日)</t>
+(25年-07月-24日)</t>
         </is>
       </c>
       <c r="F8" s="21" t="inlineStr"/>
@@ -29383,7 +29407,7 @@
           <t>A | 968呎 (3房)
 $11280万
 $116,529/呎
-(25年-05月-27日)</t>
+(25年-05月-28日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -29391,7 +29415,7 @@
           <t>B | 591呎 (2房)
 $11280万
 $190,863/呎
-(25年-05月-27日)</t>
+(25年-05月-28日)</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
@@ -29399,7 +29423,7 @@
           <t>C | 591呎 (2房)
 $11280万
 $190,863/呎
-(25年-05月-27日)</t>
+(25年-05月-28日)</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -29407,7 +29431,7 @@
           <t>D | 996呎 (3房)
 $11280万
 $113,253/呎
-(25年-05月-27日)</t>
+(25年-05月-28日)</t>
         </is>
       </c>
       <c r="F9" s="21" t="inlineStr"/>
@@ -29425,7 +29449,7 @@
           <t>A | 968呎 (3房)
 $3509万
 $36,250/呎
-(25年-04月-27日)</t>
+(25年-04月-28日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -29433,7 +29457,7 @@
           <t>B | 591呎 (2房)
 $2002万
 $33,871/呎
-(26年-03月-31日)</t>
+(26年-04月-01日)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -29441,7 +29465,7 @@
           <t>C | 591呎 (2房)
 $2002万
 $33,871/呎
-(25年-11月-12日)</t>
+(25年-11月-13日)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -29449,7 +29473,7 @@
           <t>D | 996呎 (3房)
 $3884万
 $39,000/呎
-(26年-02月-12日)</t>
+(26年-02月-13日)</t>
         </is>
       </c>
       <c r="F10" s="21" t="inlineStr"/>
@@ -29467,7 +29491,7 @@
           <t>A | 968呎 (3房)
 $3320万
 $34,298/呎
-(25年-08月-25日)</t>
+(25年-08月-26日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -29475,7 +29499,7 @@
           <t>B | 591呎 (2房)
 $1970万
 $33,337/呎
-(25年-12月-09日)</t>
+(25年-12月-10日)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -29483,7 +29507,7 @@
           <t>C | 591呎 (2房)
 $1970万
 $33,337/呎
-(25年-07月-29日)</t>
+(25年-07月-30日)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -29491,7 +29515,7 @@
           <t>D | 996呎 (3房)
 $3830万
 $38,454/呎
-(25年-11月-19日)</t>
+(25年-11月-20日)</t>
         </is>
       </c>
       <c r="F11" s="21" t="inlineStr"/>
@@ -29509,7 +29533,7 @@
           <t>A | 968呎 (3房)
 $3272万
 $33,800/呎
-(25年-12月-21日)</t>
+(25年-12月-22日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -29517,7 +29541,7 @@
           <t>B | 591呎 (2房)
 $1939万
 $32,813/呎
-(25年-11月-19日)</t>
+(25年-11月-20日)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -29525,7 +29549,7 @@
           <t>C | 591呎 (2房)
 $1939万
 $32,813/呎
-(25年-11月-05日)</t>
+(25年-11月-06日)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -29533,7 +29557,7 @@
           <t>D | 996呎 (3房)
 $3795万
 $38,100/呎
-(24年-04月-11日)</t>
+(24年-04月-12日)</t>
         </is>
       </c>
       <c r="F12" s="21" t="inlineStr"/>
@@ -29551,7 +29575,7 @@
           <t>A | 968呎 (3房)
 $3223万
 $33,300/呎
-(25年-11月-04日)</t>
+(25年-11月-05日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -29559,7 +29583,7 @@
           <t>B | 525呎 (2房)
 $1909万
 $36,356/呎
-(26年-03月-04日)</t>
+(26年-03月-05日)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -29567,7 +29591,7 @@
           <t>C | 591呎 (2房)
 $1909万
 $32,296/呎
-(25年-10月-13日)</t>
+(25年-10月-14日)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -29575,7 +29599,7 @@
           <t>D | 996呎 (3房)
 $3792万
 $38,071/呎
-(23年-06月-13日)</t>
+(23年-06月-14日)</t>
         </is>
       </c>
       <c r="F13" s="21" t="inlineStr"/>
@@ -29593,7 +29617,7 @@
           <t>A | 968呎 (3房)
 $3293万
 $34,021/呎
-(26年-02月-01日)</t>
+(26年-02月-02日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -29601,7 +29625,7 @@
           <t>B | 591呎 (2房)
 $1879万
 $31,788/呎
-(25年-08月-27日)</t>
+(25年-08月-28日)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -29609,7 +29633,7 @@
           <t>C | 591呎 (2房)
 $1879万
 $31,788/呎
-(25年-10月-15日)</t>
+(25年-10月-16日)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -29617,7 +29641,7 @@
           <t>D | 996呎 (3房)
 $3741万
 $37,563/呎
-(23年-08月-01日)</t>
+(23年-08月-02日)</t>
         </is>
       </c>
       <c r="F14" s="21" t="inlineStr"/>
@@ -29635,7 +29659,7 @@
           <t>A | 968呎 (3房)
 $3533万
 $36,500/呎
-(25年-08月-26日)</t>
+(25年-08月-27日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -29643,7 +29667,7 @@
           <t>B | 591呎 (2房)
 $1956万
 $33,093/呎
-(25年-12月-15日)</t>
+(25年-12月-16日)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -29651,7 +29675,7 @@
           <t>C | 591呎 (2房)
 $2081万
 $35,212/呎
-(25年-08月-06日)</t>
+(25年-08月-07日)</t>
         </is>
       </c>
       <c r="E15" s="20" t="inlineStr">
@@ -29677,7 +29701,7 @@
           <t>A | 968呎 (3房)
 $3175万
 $32,800/呎
-(26年-03月-03日)</t>
+(26年-03月-04日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -29685,7 +29709,7 @@
           <t>B | 591呎 (2房)
 $1891万
 $31,995/呎
-(25年-09月-17日)</t>
+(25年-09月-18日)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -29693,7 +29717,7 @@
           <t>C | 591呎 (2房)
 $1891万
 $31,995/呎
-(25年-09月-17日)</t>
+(25年-09月-18日)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -29701,7 +29725,7 @@
           <t>D | 996呎 (3房)
 $3486万
 $35,000/呎
-(25年-10月-13日)</t>
+(25年-10月-14日)</t>
         </is>
       </c>
       <c r="F16" s="21" t="inlineStr"/>
@@ -29719,7 +29743,7 @@
           <t>A | 968呎 (3房)
 $3078万
 $31,798/呎
-(25年-09月-25日)</t>
+(25年-09月-26日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -29727,7 +29751,7 @@
           <t>B | 591呎 (2房)
 $1853万
 $31,346/呎
-(26年-03月-25日)</t>
+(26年-03月-26日)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -29735,7 +29759,7 @@
           <t>C | 591呎 (2房)
 $1853万
 $31,346/呎
-(25年-10月-15日)</t>
+(25年-10月-16日)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -29743,7 +29767,7 @@
           <t>D | 996呎 (3房)
 $3436万
 $34,500/呎
-(25年-08月-10日)</t>
+(25年-08月-11日)</t>
         </is>
       </c>
       <c r="F17" s="21" t="inlineStr"/>
@@ -29761,7 +29785,7 @@
           <t>A | 968呎 (3房)
 $3030万
 $31,300/呎
-(26年-02月-25日)</t>
+(26年-02月-26日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -29769,7 +29793,7 @@
           <t>B | 591呎 (2房)
 $1842万
 $31,159/呎
-(25年-11月-12日)</t>
+(25年-11月-13日)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -29777,7 +29801,7 @@
           <t>C | 591呎 (2房)
 $1842万
 $31,159/呎
-(25年-11月-03日)</t>
+(25年-11月-04日)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -29785,7 +29809,7 @@
           <t>D | 996呎 (3房)
 $3436万
 $34,500/呎
-(26年-03月-29日)</t>
+(26年-03月-30日)</t>
         </is>
       </c>
       <c r="F18" s="21" t="inlineStr"/>
@@ -29803,7 +29827,7 @@
           <t>A | 968呎 (3房)
 $2981万
 $30,800/呎
-(25年-12月-07日)</t>
+(25年-12月-08日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -29811,7 +29835,7 @@
           <t>B | 591呎 (2房)
 $1832万
 $31,004/呎
-(26年-04月-01日)</t>
+(26年-04月-02日)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -29819,7 +29843,7 @@
           <t>C | 591呎 (2房)
 $1832万
 $31,004/呎
-(25年-12月-22日)</t>
+(25年-12月-23日)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -29827,7 +29851,7 @@
           <t>D | 996呎 (3房)
 $3406万
 $34,200/呎
-(26年-04月-20日)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="F19" s="21" t="inlineStr"/>
@@ -29845,7 +29869,7 @@
           <t>A | 968呎 (3房)
 $2933万
 $30,300/呎
-(26年-03月-04日)</t>
+(26年-03月-05日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -29853,7 +29877,7 @@
           <t>B | 591呎 (2房)
 $1934万
 $32,726/呎
-(26年-06月-10日)</t>
+(26年-06月-11日)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -29861,7 +29885,7 @@
           <t>C | 591呎 (2房)
 $1866万
 $31,576/呎
-(25年-04月-23日)</t>
+(25年-04月-24日)</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
@@ -29869,7 +29893,7 @@
           <t>D | 996呎 (3房)
 $3685万
 $37,000/呎
-(26年-07月-21日)</t>
+(26年-07月-22日)</t>
         </is>
       </c>
       <c r="F20" s="21" t="inlineStr"/>
@@ -29887,7 +29911,7 @@
           <t>A | 968呎 (3房)
 $2885万
 $29,800/呎
-(26年-01月-11日)</t>
+(26年-01月-12日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -29895,7 +29919,7 @@
           <t>B | 591呎 (2房)
 $1924万
 $32,563/呎
-(26年-06月-15日)</t>
+(26年-06月-16日)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -29903,7 +29927,7 @@
           <t>C | 591呎 (2房)
 $1814万
 $30,696/呎
-(26年-04月-01日)</t>
+(26年-04月-02日)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -29911,7 +29935,7 @@
           <t>D | 996呎 (3房)
 $3546万
 $35,600/呎
-(26年-06月-21日)</t>
+(26年-06月-22日)</t>
         </is>
       </c>
       <c r="F21" s="21" t="inlineStr"/>
@@ -29929,7 +29953,7 @@
           <t>A | 968呎 (3房)
 $2885万
 $29,800/呎
-(26年-03月-26日)</t>
+(26年-03月-27日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -29937,7 +29961,7 @@
           <t>B | 591呎 (2房)
 $1906万
 $32,242/呎
-(26年-07月-01日)</t>
+(26年-07月-30日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -29945,7 +29969,7 @@
           <t>C | 591呎 (2房)
 $1796万
 $30,393/呎
-(26年-04月-01日)</t>
+(26年-04月-02日)</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
@@ -29971,7 +29995,7 @@
           <t>A | 968呎 (3房)
 $2875万
 $29,700/呎
-(26年-05月-31日)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -29979,7 +30003,7 @@
           <t>B | 591呎 (2房)
 $1817万
 $30,748/呎
-(26年-05月-20日)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -29987,7 +30011,7 @@
           <t>C | 591呎 (2房)
 $1747万
 $29,564/呎
-(26年-04月-22日)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="E23" s="20" t="inlineStr">
@@ -30013,7 +30037,7 @@
           <t>A | 968呎 (3房)
 $2768万
 $28,600/呎
-(25年-10月-16日)</t>
+(25年-10月-17日)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -30021,7 +30045,7 @@
           <t>B | 591呎 (2房)
 $1685万
 $28,505/呎
-(25年-05月-15日)</t>
+(25年-05月-16日)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -30029,7 +30053,7 @@
           <t>C | 591呎 (2房)
 $1685万
 $28,505/呎
-(25年-05月-06日)</t>
+(25年-05月-07日)</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
@@ -30055,7 +30079,7 @@
           <t>A | 968呎 (3房)
 $2860万
 $29,550/呎
-(26年-06月-21日)</t>
+(26年-06月-22日)</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
@@ -30071,7 +30095,7 @@
           <t>C | 591呎 (2房)
 $1663万
 $28,141/呎
-(25年-12月-04日)</t>
+(25年-12月-05日)</t>
         </is>
       </c>
       <c r="E25" s="20" t="inlineStr">
@@ -30097,7 +30121,7 @@
           <t>A | 968呎 (3房)
 $2681万
 $27,700/呎
-(26年-01月-21日)</t>
+(26年-01月-22日)</t>
         </is>
       </c>
       <c r="C26" s="22" t="inlineStr">
@@ -30105,7 +30129,7 @@
           <t>B | 591呎 (2房)
 $1671万
 $28,279/呎
-(26年-05月-06日)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
       <c r="D26" s="22" t="inlineStr">
@@ -30113,7 +30137,7 @@
           <t>C | 591呎 (2房)
 $1623万
 $27,454/呎
-(26年-03月-23日)</t>
+(26年-03月-24日)</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
@@ -30155,7 +30179,7 @@
           <t>C | 591呎 (2房)
 $1583万
 $26,784/呎
-(26年-04月-09日)</t>
+(26年-04月-10日)</t>
         </is>
       </c>
       <c r="E27" s="20" t="inlineStr">
@@ -30189,7 +30213,7 @@
           <t>B | 591呎 (2房)
 $1583万
 $26,785/呎
-(26年-04月-22日)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="D28" s="22" t="inlineStr">
@@ -30197,7 +30221,7 @@
           <t>C | 591呎 (2房)
 $1537万
 $26,005/呎
-(26年-04月-07日)</t>
+(26年-04月-08日)</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
@@ -30231,7 +30255,7 @@
           <t>B | 548呎 (2房)
 $1660万
 $30,292/呎
-(25年-11月-13日)</t>
+(25年-11月-14日)</t>
         </is>
       </c>
       <c r="D29" s="22" t="inlineStr">
@@ -30239,7 +30263,7 @@
           <t>C | 548呎 (2房)
 $1708万
 $31,168/呎
-(25年-05月-28日)</t>
+(25年-05月-29日)</t>
         </is>
       </c>
       <c r="E29" s="22" t="inlineStr">
@@ -30247,7 +30271,7 @@
           <t>D | 953呎 (3房)
 $3383万
 $35,500/呎
-(23年-07月-04日)</t>
+(23年-07月-05日)</t>
         </is>
       </c>
       <c r="F29" s="21" t="inlineStr"/>
@@ -30264,28 +30288,28 @@
       <c r="C30" s="21" t="inlineStr"/>
       <c r="D30" s="21" t="inlineStr"/>
       <c r="E30" s="21" t="inlineStr"/>
-      <c r="F30" s="23" t="inlineStr">
+      <c r="F30" s="20" t="inlineStr">
         <is>
           <t>MAISON A | 1108呎 (3房)
+招标单位
 -
+(在售)</t>
+        </is>
+      </c>
+      <c r="G30" s="20" t="inlineStr">
+        <is>
+          <t>MAISON B | 967呎 (3房)
+招标单位
 -
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="G30" s="23" t="inlineStr">
-        <is>
-          <t>MAISON B | 967呎 (3房)
+(在售)</t>
+        </is>
+      </c>
+      <c r="H30" s="20" t="inlineStr">
+        <is>
+          <t>MAISON C | 967呎 (3房)
+招标单位
 -
--
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="H30" s="23" t="inlineStr">
-        <is>
-          <t>MAISON C | 967呎 (3房)
--
--
-(暂停销售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -30362,7 +30386,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -30372,7 +30396,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>123</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -30437,7 +30461,7 @@
           <t>B | 333呎 (1房)
 $835万
 $25,061/呎
-(25年-04月-23日)</t>
+(25年-04月-24日)</t>
         </is>
       </c>
       <c r="D5" s="22" t="inlineStr">
@@ -30445,7 +30469,7 @@
           <t>C | 338呎 (1房)
 $839万
 $24,820/呎
-(25年-04月-28日)</t>
+(25年-04月-29日)</t>
         </is>
       </c>
       <c r="E5" s="22" t="inlineStr">
@@ -30453,7 +30477,7 @@
           <t>D | 541呎 (2房)
 $1460万
 $26,995/呎
-(25年-04月-23日)</t>
+(25年-04月-24日)</t>
         </is>
       </c>
       <c r="F5" s="22" t="inlineStr">
@@ -30461,7 +30485,7 @@
           <t>E | 364呎 (1房)
 $987万
 $27,116/呎
-(23年-12月-20日)</t>
+(23年-12月-21日)</t>
         </is>
       </c>
     </row>
@@ -30476,7 +30500,7 @@
           <t>A | 959呎 (3房)
 $2976万
 $31,032/呎
-(26年-01月-08日)</t>
+(26年-01月-09日)</t>
         </is>
       </c>
       <c r="C6" s="22" t="inlineStr">
@@ -30484,7 +30508,7 @@
           <t>B | 333呎 (1房)
 $775万
 $23,260/呎
-(25年-04月-29日)</t>
+(25年-04月-30日)</t>
         </is>
       </c>
       <c r="D6" s="22" t="inlineStr">
@@ -30492,7 +30516,7 @@
           <t>C | 338呎 (1房)
 $779万
 $23,058/呎
-(25年-05月-06日)</t>
+(25年-05月-07日)</t>
         </is>
       </c>
       <c r="E6" s="22" t="inlineStr">
@@ -30500,7 +30524,7 @@
           <t>D | 541呎 (2房)
 $1373万
 $25,380/呎
-(25年-04月-24日)</t>
+(25年-04月-25日)</t>
         </is>
       </c>
       <c r="F6" s="22" t="inlineStr">
@@ -30508,7 +30532,7 @@
           <t>E | 364呎 (1房)
 $893万
 $24,524/呎
-(23年-06月-12日)</t>
+(23年-06月-13日)</t>
         </is>
       </c>
     </row>
@@ -30523,7 +30547,7 @@
           <t>A | 960呎 (3房)
 $3201万
 $33,348/呎
-(24年-03月-25日)</t>
+(24年-03月-26日)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -30531,7 +30555,7 @@
           <t>B | 333呎 (1房)
 $770万
 $23,119/呎
-(25年-04月-29日)</t>
+(25年-04月-30日)</t>
         </is>
       </c>
       <c r="D7" s="22" t="inlineStr">
@@ -30539,7 +30563,7 @@
           <t>C | 338呎 (1房)
 $775万
 $22,918/呎
-(25年-05月-06日)</t>
+(25年-05月-07日)</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -30547,7 +30571,7 @@
           <t>D | 541呎 (2房)
 $1360万
 $25,130/呎
-(25年-05月-13日)</t>
+(25年-05月-14日)</t>
         </is>
       </c>
       <c r="F7" s="22" t="inlineStr">
@@ -30555,7 +30579,7 @@
           <t>E | 364呎 (1房)
 $765万
 $21,026/呎
-(25年-05月-22日)</t>
+(25年-05月-23日)</t>
         </is>
       </c>
     </row>
@@ -30570,7 +30594,7 @@
           <t>A | 959呎 (3房)
 $2880万
 $30,031/呎
-(25年-09月-22日)</t>
+(25年-09月-23日)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -30578,7 +30602,7 @@
           <t>B | 333呎 (1房)
 $768万
 $23,048/呎
-(25年-04月-24日)</t>
+(25年-04月-25日)</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr">
@@ -30586,7 +30610,7 @@
           <t>C | 338呎 (1房)
 $772万
 $22,851/呎
-(25年-05月-05日)</t>
+(25年-05月-06日)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -30594,7 +30618,7 @@
           <t>D | 541呎 (2房)
 $1394万
 $25,769/呎
-(25年-04月-27日)</t>
+(25年-04月-28日)</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
@@ -30602,7 +30626,7 @@
           <t>E | 364呎 (1房)
 $887万
 $24,377/呎
-(23年-09月-26日)</t>
+(23年-09月-27日)</t>
         </is>
       </c>
     </row>
@@ -30617,7 +30641,7 @@
           <t>A | 960呎 (3房)
 $2832万
 $29,500/呎
-(25年-06月-15日)</t>
+(25年-06月-16日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -30625,7 +30649,7 @@
           <t>B | 333呎 (1房)
 $765万
 $22,980/呎
-(25年-04月-24日)</t>
+(25年-04月-25日)</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
@@ -30633,7 +30657,7 @@
           <t>C | 338呎 (1房)
 $770万
 $22,782/呎
-(25年-04月-27日)</t>
+(25年-04月-28日)</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -30641,7 +30665,7 @@
           <t>D | 541呎 (2房)
 $1333万
 $24,635/呎
-(25年-04月-23日)</t>
+(25年-04月-24日)</t>
         </is>
       </c>
       <c r="F9" s="22" t="inlineStr">
@@ -30649,7 +30673,7 @@
           <t>E | 364呎 (1房)
 $895万
 $24,590/呎
-(23年-12月-18日)</t>
+(23年-12月-19日)</t>
         </is>
       </c>
     </row>
@@ -30664,7 +30688,7 @@
           <t>A | 960呎 (3房)
 $3098万
 $32,266/呎
-(24年-05月-07日)</t>
+(24年-05月-08日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -30672,7 +30696,7 @@
           <t>B | 333呎 (1房)
 $763万
 $22,912/呎
-(25年-04月-23日)</t>
+(25年-04月-24日)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -30680,7 +30704,7 @@
           <t>C | 338呎 (1房)
 $768万
 $22,715/呎
-(25年-04月-24日)</t>
+(25年-04月-25日)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -30688,7 +30712,7 @@
           <t>D | 541呎 (2房)
 $1320万
 $24,391/呎
-(25年-04月-23日)</t>
+(25年-04月-24日)</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
@@ -30696,7 +30720,7 @@
           <t>E | 364呎 (1房)
 $913万
 $25,085/呎
-(23年-06月-08日)</t>
+(23年-06月-09日)</t>
         </is>
       </c>
     </row>
@@ -30711,7 +30735,7 @@
           <t>A | 960呎 (3房)
 $2736万
 $28,500/呎
-(25年-04月-29日)</t>
+(25年-04月-30日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -30719,7 +30743,7 @@
           <t>B | 333呎 (1房)
 $761万
 $22,841/呎
-(25年-04月-29日)</t>
+(25年-04月-30日)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -30727,7 +30751,7 @@
           <t>C | 338呎 (1房)
 $765万
 $22,645/呎
-(25年-05月-06日)</t>
+(25年-05月-07日)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -30735,7 +30759,7 @@
           <t>D | 541呎 (2房)
 $1307万
 $24,150/呎
-(25年-04月-23日)</t>
+(25年-04月-24日)</t>
         </is>
       </c>
       <c r="F11" s="22" t="inlineStr">
@@ -30743,7 +30767,7 @@
           <t>E | 365呎 (1房)
 $910万
 $24,941/呎
-(23年-06月-12日)</t>
+(23年-06月-13日)</t>
         </is>
       </c>
     </row>
@@ -30758,7 +30782,7 @@
           <t>A | 960呎 (3房)
 $2771万
 $28,866/呎
-(25年-05月-18日)</t>
+(25年-05月-19日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -30766,7 +30790,7 @@
           <t>B | 333呎 (1房)
 $758万
 $22,776/呎
-(25年-05月-06日)</t>
+(25年-05月-07日)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -30774,7 +30798,7 @@
           <t>C | 338呎 (1房)
 $763万
 $22,578/呎
-(25年-05月-06日)</t>
+(25年-05月-07日)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -30782,7 +30806,7 @@
           <t>D | 541呎 (2房)
 $1294万
 $23,911/呎
-(25年-04月-24日)</t>
+(25年-04月-25日)</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
@@ -30790,7 +30814,7 @@
           <t>E | 364呎 (1房)
 $908万
 $24,937/呎
-(23年-06月-13日)</t>
+(23年-06月-14日)</t>
         </is>
       </c>
     </row>
@@ -30805,7 +30829,7 @@
           <t>A | 960呎 (3房)
 $2659万
 $27,700/呎
-(25年-06月-01日)</t>
+(25年-06月-02日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -30813,7 +30837,7 @@
           <t>B | 333呎 (1房)
 $764万
 $22,942/呎
-(24年-07月-15日)</t>
+(24年-07月-16日)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -30821,7 +30845,7 @@
           <t>C | 943呎 (1房)
 $761万
 $8,069/呎
-(25年-04月-29日)</t>
+(25年-04月-30日)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -30829,7 +30853,7 @@
           <t>D | 541呎 (2房)
 $1281万
 $23,674/呎
-(25年-04月-29日)</t>
+(25年-04月-30日)</t>
         </is>
       </c>
       <c r="F13" s="22" t="inlineStr">
@@ -30837,7 +30861,7 @@
           <t>E | 364呎 (1房)
 $905万
 $24,862/呎
-(23年-06月-14日)</t>
+(23年-06月-15日)</t>
         </is>
       </c>
     </row>
@@ -30847,12 +30871,12 @@
           <t>19</t>
         </is>
       </c>
-      <c r="B14" s="22" t="inlineStr">
+      <c r="B14" s="20" t="inlineStr">
         <is>
           <t>A | 960呎 (3房)
-$2707万
-$28,196/呎
-(25年-06月-15日)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -30860,7 +30884,7 @@
           <t>B | 333呎 (1房)
 $762万
 $22,871/呎
-(24年-07月-10日)</t>
+(24年-07月-11日)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -30868,10 +30892,57 @@
           <t>C | 338呎 (1房)
 $759万
 $22,441/呎
-(25年-05月-01日)</t>
+(25年-05月-02日)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
+        <is>
+          <t>D | 541呎 (2房)
+$1253万
+$23,160/呎
+(25年-04月-25日)</t>
+        </is>
+      </c>
+      <c r="F14" s="22" t="inlineStr">
+        <is>
+          <t>E | 364呎 (1房)
+$872万
+$23,942/呎
+(23年-06月-14日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>A | 960呎 (3房)
+$2592万
+$27,000/呎
+(25年-05月-30日)</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>B | 333呎 (1房)
+$757万
+$22,742/呎
+(24年-11月-21日)</t>
+        </is>
+      </c>
+      <c r="D15" s="22" t="inlineStr">
+        <is>
+          <t>C | 338呎 (1房)
+$759万
+$22,441/呎
+(25年-04月-24日)</t>
+        </is>
+      </c>
+      <c r="E15" s="22" t="inlineStr">
         <is>
           <t>D | 541呎 (2房)
 $1253万
@@ -30879,59 +30950,12 @@
 (25年-04月-24日)</t>
         </is>
       </c>
-      <c r="F14" s="22" t="inlineStr">
-        <is>
-          <t>E | 364呎 (1房)
-$872万
-$23,942/呎
-(23年-06月-13日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="58" customHeight="1">
-      <c r="A15" s="19" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="B15" s="22" t="inlineStr">
-        <is>
-          <t>A | 960呎 (3房)
-$2592万
-$27,000/呎
-(25年-05月-29日)</t>
-        </is>
-      </c>
-      <c r="C15" s="22" t="inlineStr">
-        <is>
-          <t>B | 333呎 (1房)
-$757万
-$22,742/呎
-(24年-11月-20日)</t>
-        </is>
-      </c>
-      <c r="D15" s="22" t="inlineStr">
-        <is>
-          <t>C | 338呎 (1房)
-$759万
-$22,441/呎
-(25年-04月-23日)</t>
-        </is>
-      </c>
-      <c r="E15" s="22" t="inlineStr">
-        <is>
-          <t>D | 541呎 (2房)
-$1253万
-$23,160/呎
-(25年-04月-23日)</t>
-        </is>
-      </c>
       <c r="F15" s="22" t="inlineStr">
         <is>
           <t>E | 364呎 (1房)
 $902万
 $24,787/呎
-(23年-06月-18日)</t>
+(23年-06月-19日)</t>
         </is>
       </c>
     </row>
@@ -30946,7 +30970,7 @@
           <t>A | 960呎 (3房)
 $3058万
 $31,854/呎
-(23年-08月-08日)</t>
+(23年-08月-09日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -30954,7 +30978,7 @@
           <t>B | 333呎 (1房)
 $749万
 $22,503/呎
-(25年-05月-01日)</t>
+(25年-05月-02日)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -30962,7 +30986,7 @@
           <t>C | 338呎 (1房)
 $754万
 $22,309/呎
-(25年-04月-29日)</t>
+(25年-04月-30日)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -30970,7 +30994,7 @@
           <t>D | 541呎 (2房)
 $1228万
 $22,700/呎
-(25年-04月-22日)</t>
+(25年-04月-23日)</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
@@ -30978,7 +31002,7 @@
           <t>E | 365呎 (1房)
 $897万
 $24,570/呎
-(23年-07月-11日)</t>
+(23年-07月-12日)</t>
         </is>
       </c>
     </row>
@@ -30993,7 +31017,7 @@
           <t>A | 960呎 (3房)
 $2544万
 $26,500/呎
-(25年-05月-05日)</t>
+(25年-05月-06日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -31001,7 +31025,7 @@
           <t>B | 333呎 (1房)
 $747万
 $22,438/呎
-(25年-04月-22日)</t>
+(25年-04月-23日)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -31009,7 +31033,7 @@
           <t>C | 338呎 (1房)
 $752万
 $22,240/呎
-(25年-05月-08日)</t>
+(25年-05月-09日)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -31017,7 +31041,7 @@
           <t>D | 541呎 (2房)
 $1209万
 $22,355/呎
-(25年-04月-29日)</t>
+(25年-04月-30日)</t>
         </is>
       </c>
       <c r="F17" s="22" t="inlineStr">
@@ -31025,7 +31049,7 @@
           <t>E | 364呎 (1房)
 $894万
 $24,567/呎
-(23年-06月-13日)</t>
+(23年-06月-14日)</t>
         </is>
       </c>
     </row>
@@ -31040,7 +31064,7 @@
           <t>A | 960呎 (3房)
 $2515万
 $26,200/呎
-(25年-05月-05日)</t>
+(25年-05月-06日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -31048,7 +31072,7 @@
           <t>B | 333呎 (1房)
 $745万
 $22,370/呎
-(25年-04月-29日)</t>
+(25年-04月-30日)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -31056,7 +31080,7 @@
           <t>C | 338呎 (1房)
 $749万
 $22,173/呎
-(25年-05月-06日)</t>
+(25年-05月-07日)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -31064,7 +31088,7 @@
           <t>D | 541呎 (2房)
 $1191万
 $22,014/呎
-(25年-04月-29日)</t>
+(25年-04月-30日)</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
@@ -31072,7 +31096,7 @@
           <t>E | 364呎 (1房)
 $861万
 $23,657/呎
-(24年-04月-08日)</t>
+(24年-04月-09日)</t>
         </is>
       </c>
     </row>
@@ -31087,7 +31111,7 @@
           <t>A | 959呎 (3房)
 $2486万
 $25,927/呎
-(25年-09月-16日)</t>
+(25年-09月-17日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -31095,7 +31119,7 @@
           <t>B | 333呎 (1房)
 $746万
 $22,400/呎
-(24年-11月-11日)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -31103,7 +31127,7 @@
           <t>C | 338呎 (1房)
 $747万
 $22,108/呎
-(25年-05月-07日)</t>
+(25年-05月-08日)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -31111,7 +31135,7 @@
           <t>D | 541呎 (2房)
 $1173万
 $21,674/呎
-(25年-04月-28日)</t>
+(25年-04月-29日)</t>
         </is>
       </c>
       <c r="F19" s="22" t="inlineStr">
@@ -31119,7 +31143,7 @@
           <t>E | 364呎 (1房)
 $888万
 $24,396/呎
-(23年-07月-17日)</t>
+(23年-07月-18日)</t>
         </is>
       </c>
     </row>
@@ -31134,7 +31158,7 @@
           <t>A | 960呎 (3房)
 $2477万
 $25,800/呎
-(25年-10月-19日)</t>
+(25年-10月-20日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -31142,7 +31166,7 @@
           <t>B | 333呎 (1房)
 $740万
 $22,236/呎
-(25年-04月-28日)</t>
+(25年-04月-29日)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -31150,7 +31174,7 @@
           <t>C | 338呎 (1房)
 $745万
 $22,044/呎
-(25年-04月-24日)</t>
+(25年-04月-25日)</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
@@ -31158,7 +31182,7 @@
           <t>D | 541呎 (2房)
 $1169万
 $21,609/呎
-(25年-05月-06日)</t>
+(25年-05月-07日)</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
@@ -31166,7 +31190,7 @@
           <t>E | 364呎 (1房)
 $854万
 $23,468/呎
-(23年-06月-13日)</t>
+(23年-06月-14日)</t>
         </is>
       </c>
     </row>
@@ -31181,7 +31205,7 @@
           <t>A | 960呎 (3房)
 $2867万
 $29,862/呎
-(23年-06月-13日)</t>
+(23年-06月-14日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -31189,7 +31213,7 @@
           <t>B | 333呎 (1房)
 $738万
 $22,170/呎
-(25年-04月-24日)</t>
+(25年-04月-25日)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -31197,7 +31221,7 @@
           <t>C | 338呎 (1房)
 $743万
 $21,977/呎
-(25年-04月-23日)</t>
+(25年-04月-24日)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -31205,7 +31229,7 @@
           <t>D | 541呎 (2房)
 $1166万
 $21,543/呎
-(25年-04月-23日)</t>
+(25年-04月-24日)</t>
         </is>
       </c>
       <c r="F21" s="22" t="inlineStr">
@@ -31213,7 +31237,7 @@
           <t>E | 364呎 (1房)
 $880万
 $24,176/呎
-(23年-06月-13日)</t>
+(23年-06月-14日)</t>
         </is>
       </c>
     </row>
@@ -31228,7 +31252,7 @@
           <t>A | 960呎 (3房)
 $2924万
 $30,459/呎
-(23年-06月-12日)</t>
+(23年-06月-13日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -31236,7 +31260,7 @@
           <t>B | 333呎 (1房)
 $736万
 $22,102/呎
-(25年-05月-05日)</t>
+(25年-05月-06日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -31244,7 +31268,7 @@
           <t>C | 338呎 (1房)
 $741万
 $21,909/呎
-(25年-05月-07日)</t>
+(25年-05月-08日)</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -31252,7 +31276,7 @@
           <t>D | 541呎 (2房)
 $1147万
 $21,208/呎
-(25年-04月-24日)</t>
+(25年-04月-25日)</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
@@ -31260,7 +31284,7 @@
           <t>E | 364呎 (1房)
 $738万
 $20,262/呎
-(25年-05月-29日)</t>
+(25年-05月-30日)</t>
         </is>
       </c>
     </row>
@@ -31275,7 +31299,7 @@
           <t>A | 960呎 (3房)
 $2764万
 $28,788/呎
-(24年-05月-01日)</t>
+(24年-05月-02日)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -31283,7 +31307,7 @@
           <t>B | 333呎 (1房)
 $741万
 $22,266/呎
-(24年-07月-15日)</t>
+(24年-07月-16日)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -31291,7 +31315,7 @@
           <t>C | 338呎 (1房)
 $750万
 $22,199/呎
-(24年-11月-25日)</t>
+(24年-11月-26日)</t>
         </is>
       </c>
       <c r="E23" s="22" t="inlineStr">
@@ -31299,7 +31323,7 @@
           <t>D | 541呎 (2房)
 $1147万
 $21,208/呎
-(25年-05月-08日)</t>
+(25年-05月-09日)</t>
         </is>
       </c>
       <c r="F23" s="22" t="inlineStr">
@@ -31307,7 +31331,7 @@
           <t>E | 364呎 (1房)
 $863万
 $23,702/呎
-(23年-06月-11日)</t>
+(23年-06月-12日)</t>
         </is>
       </c>
     </row>
@@ -31322,7 +31346,7 @@
           <t>A | 960呎 (3房)
 $2256万
 $23,500/呎
-(25年-05月-19日)</t>
+(25年-05月-20日)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -31330,7 +31354,7 @@
           <t>B | 333呎 (1房)
 $737万
 $22,129/呎
-(24年-11月-24日)</t>
+(24年-11月-25日)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -31338,7 +31362,7 @@
           <t>C | 338呎 (1房)
 $736万
 $21,780/呎
-(25年-04月-28日)</t>
+(25年-04月-29日)</t>
         </is>
       </c>
       <c r="E24" s="22" t="inlineStr">
@@ -31346,7 +31370,7 @@
           <t>D | 541呎 (2房)
 $1144万
 $21,144/呎
-(25年-05月-01日)</t>
+(25年-05月-02日)</t>
         </is>
       </c>
       <c r="F24" s="22" t="inlineStr">
@@ -31354,7 +31378,7 @@
           <t>E | 364呎 (1房)
 $859万
 $23,586/呎
-(23年-06月-14日)</t>
+(23年-06月-15日)</t>
         </is>
       </c>
     </row>
@@ -31369,7 +31393,7 @@
           <t>A | 960呎 (3房)
 $2208万
 $23,000/呎
-(25年-07月-02日)</t>
+(25年-07月-03日)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -31377,7 +31401,7 @@
           <t>B | 333呎 (1房)
 $737万
 $22,130/呎
-(24年-07月-09日)</t>
+(24年-07月-10日)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -31385,7 +31409,7 @@
           <t>C | 338呎 (1房)
 $734万
 $21,713/呎
-(25年-04月-27日)</t>
+(25年-04月-28日)</t>
         </is>
       </c>
       <c r="E25" s="22" t="inlineStr">
@@ -31393,7 +31417,7 @@
           <t>D | 541呎 (2房)
 $1126万
 $20,811/呎
-(25年-04月-29日)</t>
+(25年-04月-30日)</t>
         </is>
       </c>
       <c r="F25" s="22" t="inlineStr">
@@ -31401,7 +31425,7 @@
           <t>E | 364呎 (1房)
 $730万
 $20,059/呎
-(25年-05月-29日)</t>
+(25年-05月-30日)</t>
         </is>
       </c>
     </row>
@@ -31416,7 +31440,7 @@
           <t>A | 960呎 (3房)
 $2131万
 $22,200/呎
-(25年-06月-09日)</t>
+(25年-06月-10日)</t>
         </is>
       </c>
       <c r="C26" s="22" t="inlineStr">
@@ -31424,7 +31448,7 @@
           <t>B | 333呎 (1房)
 $727万
 $21,840/呎
-(25年-04月-28日)</t>
+(25年-04月-29日)</t>
         </is>
       </c>
       <c r="D26" s="22" t="inlineStr">
@@ -31432,7 +31456,7 @@
           <t>C | 338呎 (1房)
 $732万
 $21,649/呎
-(25年-04月-29日)</t>
+(25年-04月-30日)</t>
         </is>
       </c>
       <c r="E26" s="22" t="inlineStr">
@@ -31440,7 +31464,7 @@
           <t>D | 541呎 (2房)
 $1086万
 $20,074/呎
-(25年-05月-01日)</t>
+(25年-05月-02日)</t>
         </is>
       </c>
       <c r="F26" s="22" t="inlineStr">
@@ -31448,7 +31472,7 @@
           <t>E | 364呎 (1房)
 $727万
 $19,961/呎
-(25年-06月-18日)</t>
+(25年-06月-19日)</t>
         </is>
       </c>
     </row>
@@ -31463,7 +31487,7 @@
           <t>A | 960呎 (3房)
 $2504万
 $26,081/呎
-(24年-04月-25日)</t>
+(24年-04月-26日)</t>
         </is>
       </c>
       <c r="C27" s="22" t="inlineStr">
@@ -31471,7 +31495,7 @@
           <t>B | 333呎 (1房)
 $720万
 $21,623/呎
-(25年-04月-28日)</t>
+(25年-04月-29日)</t>
         </is>
       </c>
       <c r="D27" s="22" t="inlineStr">
@@ -31479,7 +31503,7 @@
           <t>C | 338呎 (1房)
 $721万
 $21,323/呎
-(25年-04月-22日)</t>
+(25年-04月-23日)</t>
         </is>
       </c>
       <c r="E27" s="22" t="inlineStr">
@@ -31487,7 +31511,7 @@
           <t>D | 541呎 (2房)
 $1046万
 $19,342/呎
-(25年-04月-29日)</t>
+(25年-04月-30日)</t>
         </is>
       </c>
       <c r="F27" s="22" t="inlineStr">
@@ -31495,7 +31519,7 @@
           <t>E | 364呎 (1房)
 $809万
 $22,221/呎
-(24年-06月-10日)</t>
+(24年-06月-11日)</t>
         </is>
       </c>
     </row>
@@ -31510,7 +31534,7 @@
           <t>A | 960呎 (3房)
 $2064万
 $21,500/呎
-(25年-07月-13日)</t>
+(25年-07月-14日)</t>
         </is>
       </c>
       <c r="C28" s="22" t="inlineStr">
@@ -31518,7 +31542,7 @@
           <t>B | 333呎 (1房)
 $721万
 $21,639/呎
-(24年-11月-07日)</t>
+(24年-11月-08日)</t>
         </is>
       </c>
       <c r="D28" s="22" t="inlineStr">
@@ -31526,7 +31550,7 @@
           <t>C | 338呎 (1房)
 $711万
 $21,040/呎
-(25年-05月-06日)</t>
+(25年-05月-07日)</t>
         </is>
       </c>
       <c r="E28" s="22" t="inlineStr">
@@ -31534,7 +31558,7 @@
           <t>D | 541呎 (2房)
 $1022万
 $18,888/呎
-(25年-04月-24日)</t>
+(25年-04月-25日)</t>
         </is>
       </c>
       <c r="F28" s="22" t="inlineStr">
@@ -31542,7 +31566,7 @@
           <t>E | 364呎 (1房)
 $799万
 $21,948/呎
-(24年-03月-11日)</t>
+(24年-03月-12日)</t>
         </is>
       </c>
     </row>
@@ -31557,7 +31581,7 @@
           <t>A | 916呎 (3房)
 $2843万
 $31,034/呎
-(26年-02月-05日)</t>
+(26年-02月-06日)</t>
         </is>
       </c>
       <c r="C29" s="22" t="inlineStr">
@@ -31565,7 +31589,7 @@
           <t>B | 311呎 (1房)
 $787万
 $25,308/呎
-(24年-07月-30日)</t>
+(24年-07月-31日)</t>
         </is>
       </c>
       <c r="D29" s="22" t="inlineStr">
@@ -31573,7 +31597,7 @@
           <t>C | 317呎 (1房)
 $805万
 $25,403/呎
-(24年-08月-28日)</t>
+(24年-08月-29日)</t>
         </is>
       </c>
       <c r="E29" s="22" t="inlineStr">
@@ -31581,7 +31605,7 @@
           <t>D | 504呎 (2房)
 $1143万
 $22,688/呎
-(25年-04月-29日)</t>
+(25年-04月-30日)</t>
         </is>
       </c>
       <c r="F29" s="22" t="inlineStr">
@@ -31589,7 +31613,7 @@
           <t>E | 327呎 (1房)
 $863万
 $26,400/呎
-(23年-06月-20日)</t>
+(23年-06月-21日)</t>
         </is>
       </c>
     </row>
@@ -31667,12 +31691,12 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
@@ -31682,7 +31706,7 @@
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F3" s="18" t="inlineStr">
@@ -31734,20 +31758,20 @@
           <t>29</t>
         </is>
       </c>
-      <c r="B5" s="24" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>A | 1615呎 (4+房)
 招标单位
 -
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C5" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>B | 1556呎 (4+房)
 招标单位
 -
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="D5" s="21" t="inlineStr"/>
@@ -31761,20 +31785,20 @@
           <t>28</t>
         </is>
       </c>
-      <c r="B6" s="24" t="inlineStr">
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>A | 1615呎 (4+房)
 招标单位
 -
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C6" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
         <is>
           <t>B | 1556呎 (4+房)
 招标单位
 -
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="D6" s="21" t="inlineStr"/>
@@ -31793,7 +31817,7 @@
           <t>A | 997呎 (3房)
 $3639万
 $36,500/呎
-(26年-07月-21日)</t>
+(26年-07月-22日)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -31801,10 +31825,10 @@
           <t>B | 597呎 (2房)
 $2138万
 $35,807/呎
-(26年-07月-21日)</t>
-        </is>
-      </c>
-      <c r="D7" s="25" t="inlineStr">
+(26年-07月-22日)</t>
+        </is>
+      </c>
+      <c r="D7" s="23" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 -
@@ -31812,7 +31836,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E7" s="25" t="inlineStr">
+      <c r="E7" s="23" t="inlineStr">
         <is>
           <t>D | 992呎 (3房)
 -
@@ -31842,10 +31866,10 @@
           <t>B | 597呎 (2房)
 $2152万
 $36,046/呎
-(26年-06月-09日)</t>
-        </is>
-      </c>
-      <c r="D8" s="25" t="inlineStr">
+(26年-06月-10日)</t>
+        </is>
+      </c>
+      <c r="D8" s="23" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 -
@@ -31853,7 +31877,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E8" s="25" t="inlineStr">
+      <c r="E8" s="23" t="inlineStr">
         <is>
           <t>D | 992呎 (3房)
 -
@@ -31883,10 +31907,10 @@
           <t>B | 597呎 (2房)
 $2154万
 $36,089/呎
-(26年-05月-25日)</t>
-        </is>
-      </c>
-      <c r="D9" s="25" t="inlineStr">
+(26年-05月-26日)</t>
+        </is>
+      </c>
+      <c r="D9" s="23" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 -
@@ -31894,7 +31918,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E9" s="25" t="inlineStr">
+      <c r="E9" s="23" t="inlineStr">
         <is>
           <t>D | 992呎 (3房)
 -
@@ -31924,10 +31948,10 @@
           <t>B | 597呎 (2房)
 $2022万
 $33,871/呎
-(26年-05月-26日)</t>
-        </is>
-      </c>
-      <c r="D10" s="23" t="inlineStr">
+(26年-05月-27日)</t>
+        </is>
+      </c>
+      <c r="D10" s="24" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 $2374万
@@ -31935,7 +31959,7 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="E10" s="25" t="inlineStr">
+      <c r="E10" s="23" t="inlineStr">
         <is>
           <t>D | 992呎 (3房)
 -
@@ -31957,7 +31981,7 @@
           <t>A | 997呎 (3房)
 $3420万
 $34,301/呎
-(26年-06月-02日)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -31965,7 +31989,7 @@
           <t>B | 597呎 (2房)
 $1990万
 $33,337/呎
-(26年-05月-10日)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -31976,7 +32000,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E11" s="25" t="inlineStr">
+      <c r="E11" s="23" t="inlineStr">
         <is>
           <t>D | 992呎 (3房)
 -
@@ -32006,7 +32030,7 @@
           <t>B | 597呎 (2房)
 $1959万
 $32,814/呎
-(26年-05月-28日)</t>
+(26年-05月-29日)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -32017,7 +32041,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E12" s="25" t="inlineStr">
+      <c r="E12" s="23" t="inlineStr">
         <is>
           <t>D | 992呎 (3房)
 -
@@ -32047,7 +32071,7 @@
           <t>B | 597呎 (2房)
 $1967万
 $32,942/呎
-(26年-07月-06日)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -32055,10 +32079,10 @@
           <t>C | 593呎 (2房)
 $1947万
 $32,832/呎
-(23年-12月-06日)</t>
-        </is>
-      </c>
-      <c r="E13" s="25" t="inlineStr">
+(23年-12月-07日)</t>
+        </is>
+      </c>
+      <c r="E13" s="23" t="inlineStr">
         <is>
           <t>D | 992呎 (3房)
 -
@@ -32088,7 +32112,7 @@
           <t>B | 597呎 (2房)
 $1898万
 $31,789/呎
-(26年-06月-04日)</t>
+(26年-06月-05日)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -32099,7 +32123,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E14" s="25" t="inlineStr">
+      <c r="E14" s="23" t="inlineStr">
         <is>
           <t>D | 992呎 (3房)
 -
@@ -32129,7 +32153,7 @@
           <t>B | 597呎 (2房)
 $1928万
 $32,295/呎
-(26年-07月-06日)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -32140,7 +32164,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E15" s="25" t="inlineStr">
+      <c r="E15" s="23" t="inlineStr">
         <is>
           <t>D | 992呎 (3房)
 -
@@ -32162,7 +32186,7 @@
           <t>A | 997呎 (3房)
 $3210万
 $32,201/呎
-(26年-05月-19日)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -32170,10 +32194,10 @@
           <t>B | 597呎 (2房)
 $1883万
 $31,536/呎
-(26年-05月-05日)</t>
-        </is>
-      </c>
-      <c r="D16" s="24" t="inlineStr">
+(26年-05月-06日)</t>
+        </is>
+      </c>
+      <c r="D16" s="25" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 $2215万
@@ -32181,7 +32205,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="E16" s="25" t="inlineStr">
+      <c r="E16" s="23" t="inlineStr">
         <is>
           <t>D | 992呎 (3房)
 -
@@ -32203,7 +32227,7 @@
           <t>A | 997呎 (3房)
 $3170万
 $31,800/呎
-(26年-05月-17日)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -32211,10 +32235,10 @@
           <t>B | 597呎 (2房)
 $1871万
 $31,347/呎
-(26年-05月-04日)</t>
-        </is>
-      </c>
-      <c r="D17" s="24" t="inlineStr">
+(26年-05月-05日)</t>
+        </is>
+      </c>
+      <c r="D17" s="25" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 $2202万
@@ -32222,7 +32246,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="E17" s="25" t="inlineStr">
+      <c r="E17" s="23" t="inlineStr">
         <is>
           <t>D | 992呎 (3房)
 -
@@ -32244,7 +32268,7 @@
           <t>A | 997呎 (3房)
 $3121万
 $31,300/呎
-(26年-05月-25日)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -32252,7 +32276,7 @@
           <t>B | 597呎 (2房)
 $1876万
 $31,419/呎
-(24年-04月-10日)</t>
+(24年-04月-11日)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -32263,7 +32287,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E18" s="25" t="inlineStr">
+      <c r="E18" s="23" t="inlineStr">
         <is>
           <t>D | 992呎 (3房)
 -
@@ -32285,7 +32309,7 @@
           <t>A | 997呎 (3房)
 $3071万
 $30,800/呎
-(26年-06月-04日)</t>
+(26年-06月-05日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -32293,7 +32317,7 @@
           <t>B | 597呎 (2房)
 $1851万
 $31,005/呎
-(26年-05月-05日)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -32304,7 +32328,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E19" s="25" t="inlineStr">
+      <c r="E19" s="23" t="inlineStr">
         <is>
           <t>D | 992呎 (3房)
 -
@@ -32326,7 +32350,7 @@
           <t>A | 997呎 (3房)
 $3021万
 $30,301/呎
-(26年-06月-23日)</t>
+(26年-07月-28日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -32334,7 +32358,7 @@
           <t>B | 597呎 (2房)
 $1923万
 $32,205/呎
-(23年-06月-11日)</t>
+(23年-06月-12日)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -32342,10 +32366,10 @@
           <t>C | 593呎 (2房)
 $1907万
 $32,156/呎
-(23年-06月-11日)</t>
-        </is>
-      </c>
-      <c r="E20" s="25" t="inlineStr">
+(23年-06月-12日)</t>
+        </is>
+      </c>
+      <c r="E20" s="23" t="inlineStr">
         <is>
           <t>D | 992呎 (3房)
 -
@@ -32367,7 +32391,7 @@
           <t>A | 997呎 (3房)
 $2971万
 $29,800/呎
-(26年-07月-19日)</t>
+(26年-07月-20日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -32375,7 +32399,7 @@
           <t>B | 597呎 (2房)
 $1869万
 $31,310/呎
-(26年-06月-29日)</t>
+(26年-06月-30日)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -32383,10 +32407,10 @@
           <t>C | 593呎 (2房)
 $1833万
 $30,905/呎
-(23年-07月-03日)</t>
-        </is>
-      </c>
-      <c r="E21" s="25" t="inlineStr">
+(23年-07月-04日)</t>
+        </is>
+      </c>
+      <c r="E21" s="23" t="inlineStr">
         <is>
           <t>D | 992呎 (3房)
 -
@@ -32408,7 +32432,7 @@
           <t>A | 997呎 (3房)
 $2921万
 $29,301/呎
-(26年-06月-25日)</t>
+(26年-06月-26日)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -32424,10 +32448,10 @@
           <t>C | 593呎 (2房)
 $1836万
 $30,960/呎
-(23年-11月-12日)</t>
-        </is>
-      </c>
-      <c r="E22" s="25" t="inlineStr">
+(23年-11月-13日)</t>
+        </is>
+      </c>
+      <c r="E22" s="23" t="inlineStr">
         <is>
           <t>D | 992呎 (3房)
 -
@@ -32457,7 +32481,7 @@
           <t>B | 597呎 (2房)
 $1765万
 $29,564/呎
-(26年-06月-01日)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -32465,10 +32489,10 @@
           <t>C | 593呎 (2房)
 $1786万
 $30,117/呎
-(24年-02月-06日)</t>
-        </is>
-      </c>
-      <c r="E23" s="25" t="inlineStr">
+(24年-02月-07日)</t>
+        </is>
+      </c>
+      <c r="E23" s="23" t="inlineStr">
         <is>
           <t>D | 992呎 (3房)
 -
@@ -32498,7 +32522,7 @@
           <t>B | 597呎 (2房)
 $1789万
 $29,964/呎
-(23年-06月-26日)</t>
+(23年-06月-27日)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -32509,7 +32533,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E24" s="25" t="inlineStr">
+      <c r="E24" s="23" t="inlineStr">
         <is>
           <t>D | 992呎 (3房)
 -
@@ -32539,7 +32563,7 @@
           <t>B | 597呎 (2房)
 $1680万
 $28,141/呎
-(26年-05月-21日)</t>
+(26年-05月-22日)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -32547,10 +32571,10 @@
           <t>C | 593呎 (2房)
 $1723万
 $29,047/呎
-(23年-06月-14日)</t>
-        </is>
-      </c>
-      <c r="E25" s="25" t="inlineStr">
+(23年-06月-15日)</t>
+        </is>
+      </c>
+      <c r="E25" s="23" t="inlineStr">
         <is>
           <t>D | 992呎 (3房)
 -
@@ -32580,7 +32604,7 @@
           <t>B | 597呎 (2房)
 $1657万
 $27,762/呎
-(23年-06月-13日)</t>
+(23年-06月-14日)</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -32591,7 +32615,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E26" s="25" t="inlineStr">
+      <c r="E26" s="23" t="inlineStr">
         <is>
           <t>D | 992呎 (3房)
 -
@@ -32621,7 +32645,7 @@
           <t>B | 597呎 (2房)
 $1581万
 $26,487/呎
-(24年-03月-21日)</t>
+(24年-03月-22日)</t>
         </is>
       </c>
       <c r="D27" s="22" t="inlineStr">
@@ -32629,10 +32653,10 @@
           <t>C | 593呎 (2房)
 $1624万
 $27,381/呎
-(23年-06月-12日)</t>
-        </is>
-      </c>
-      <c r="E27" s="25" t="inlineStr">
+(23年-06月-13日)</t>
+        </is>
+      </c>
+      <c r="E27" s="23" t="inlineStr">
         <is>
           <t>D | 992呎 (3房)
 -
@@ -32662,7 +32686,7 @@
           <t>B | 597呎 (2房)
 $1589万
 $26,622/呎
-(23年-07月-03日)</t>
+(23年-07月-04日)</t>
         </is>
       </c>
       <c r="D28" s="22" t="inlineStr">
@@ -32670,10 +32694,10 @@
           <t>C | 593呎 (2房)
 $1576万
 $26,584/呎
-(23年-06月-12日)</t>
-        </is>
-      </c>
-      <c r="E28" s="25" t="inlineStr">
+(23年-06月-13日)</t>
+        </is>
+      </c>
+      <c r="E28" s="23" t="inlineStr">
         <is>
           <t>D | 992呎 (3房)
 -
@@ -32698,20 +32722,20 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C29" s="23" t="inlineStr">
+      <c r="C29" s="20" t="inlineStr">
         <is>
           <t>B | 555呎 (2房)
-$1988万
-$35,823/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D29" s="23" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D29" s="20" t="inlineStr">
         <is>
           <t>C | 550呎 (2房)
-$1957万
-$35,589/呎
-(暂停销售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="E29" s="22" t="inlineStr">
@@ -32719,7 +32743,7 @@
           <t>D | 949呎 (3房)
 $3421万
 $36,048/呎
-(24年-04月-18日)</t>
+(24年-04月-19日)</t>
         </is>
       </c>
       <c r="F29" s="21" t="inlineStr"/>
@@ -32735,12 +32759,12 @@
       <c r="C30" s="21" t="inlineStr"/>
       <c r="D30" s="21" t="inlineStr"/>
       <c r="E30" s="21" t="inlineStr"/>
-      <c r="F30" s="23" t="inlineStr">
+      <c r="F30" s="20" t="inlineStr">
         <is>
           <t>MAISON D | 889呎 (3房)
+招标单位
 -
--
-(暂停销售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="G30" s="22" t="inlineStr">
@@ -32748,7 +32772,7 @@
           <t>MAISON E | 940呎 (3房)
 $2880万
 $30,638/呎
-(23年-11月-13日)</t>
+(23年-11月-14日)</t>
         </is>
       </c>
     </row>
@@ -32892,7 +32916,7 @@
           <t>A | 1144呎 (3房)
 $4777万
 $41,757/呎
-(26年-04月-26日)</t>
+(26年-04月-27日)</t>
         </is>
       </c>
       <c r="C5" s="22" t="inlineStr">
@@ -32900,7 +32924,7 @@
           <t>B | 425呎 (2房)
 $1384万
 $32,572/呎
-(25年-11月-20日)</t>
+(25年-11月-21日)</t>
         </is>
       </c>
       <c r="D5" s="22" t="inlineStr">
@@ -32908,7 +32932,7 @@
           <t>C | 425呎 (2房)
 $1357万
 $31,928/呎
-(25年-12月-15日)</t>
+(25年-12月-16日)</t>
         </is>
       </c>
       <c r="E5" s="20" t="inlineStr">
@@ -32924,7 +32948,7 @@
           <t>E | 469呎 (2房)
 $1314万
 $28,006/呎
-(26年-01月-11日)</t>
+(26年-01月-12日)</t>
         </is>
       </c>
     </row>
@@ -32947,7 +32971,7 @@
           <t>B | 525呎 (2房)
 $1399万
 $26,654/呎
-(25年-05月-12日)</t>
+(25年-05月-13日)</t>
         </is>
       </c>
       <c r="D6" s="22" t="inlineStr">
@@ -32955,7 +32979,7 @@
           <t>C | 522呎 (2房)
 $1483万
 $28,407/呎
-(25年-06月-05日)</t>
+(25年-06月-06日)</t>
         </is>
       </c>
       <c r="E6" s="22" t="inlineStr">
@@ -32963,7 +32987,7 @@
           <t>D | 936呎 (3房)
 $3064万
 $32,735/呎
-(26年-05月-28日)</t>
+(26年-05月-29日)</t>
         </is>
       </c>
       <c r="F6" s="22" t="inlineStr">
@@ -32971,7 +32995,7 @@
           <t>E | 469呎 (2房)
 $1270万
 $27,077/呎
-(23年-11月-02日)</t>
+(23年-11月-03日)</t>
         </is>
       </c>
     </row>
@@ -32994,7 +33018,7 @@
           <t>B | 525呎 (2房)
 $1437万
 $27,377/呎
-(25年-05月-14日)</t>
+(25年-05月-15日)</t>
         </is>
       </c>
       <c r="D7" s="22" t="inlineStr">
@@ -33002,7 +33026,7 @@
           <t>C | 522呎 (2房)
 $1454万
 $27,850/呎
-(25年-06月-03日)</t>
+(25年-06月-04日)</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -33010,7 +33034,7 @@
           <t>D | 936呎 (3房)
 $3017万
 $32,234/呎
-(26年-05月-25日)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="F7" s="22" t="inlineStr">
@@ -33018,7 +33042,7 @@
           <t>E | 469呎 (2房)
 $1124万
 $23,955/呎
-(25年-05月-22日)</t>
+(25年-05月-23日)</t>
         </is>
       </c>
     </row>
@@ -33033,7 +33057,7 @@
           <t>A | 957呎 (3房)
 $3067万
 $32,050/呎
-(26年-05月-14日)</t>
+(26年-05月-15日)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -33041,7 +33065,7 @@
           <t>B | 525呎 (2房)
 $1345万
 $25,621/呎
-(25年-05月-07日)</t>
+(25年-05月-08日)</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr">
@@ -33049,7 +33073,7 @@
           <t>C | 522呎 (2房)
 $1425万
 $27,303/呎
-(25年-05月-21日)</t>
+(25年-05月-22日)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -33057,7 +33081,7 @@
           <t>D | 936呎 (3房)
 $2970万
 $31,734/呎
-(26年-05月-05日)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
@@ -33065,7 +33089,7 @@
           <t>E | 469呎 (2房)
 $1117万
 $23,812/呎
-(25年-05月-08日)</t>
+(25年-05月-09日)</t>
         </is>
       </c>
     </row>
@@ -33088,7 +33112,7 @@
           <t>B | 525呎 (2房)
 $1319万
 $25,118/呎
-(25年-05月-18日)</t>
+(25年-05月-19日)</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
@@ -33096,7 +33120,7 @@
           <t>C | 522呎 (2房)
 $1410万
 $27,008/呎
-(25年-05月-27日)</t>
+(25年-05月-28日)</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -33104,7 +33128,7 @@
           <t>D | 936呎 (3房)
 $2783万
 $29,732/呎
-(25年-11月-11日)</t>
+(25年-11月-12日)</t>
         </is>
       </c>
       <c r="F9" s="22" t="inlineStr">
@@ -33112,7 +33136,7 @@
           <t>E | 469呎 (2房)
 $1110万
 $23,669/呎
-(25年-05月-21日)</t>
+(25年-05月-22日)</t>
         </is>
       </c>
     </row>
@@ -33127,7 +33151,7 @@
           <t>A | 957呎 (3房)
 $2828万
 $29,550/呎
-(25年-11月-25日)</t>
+(25年-11月-26日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -33135,7 +33159,7 @@
           <t>B | 525呎 (2房)
 $1293万
 $24,626/呎
-(25年-05月-11日)</t>
+(25年-05月-12日)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -33143,7 +33167,7 @@
           <t>C | 522呎 (2房)
 $1385万
 $26,537/呎
-(25年-05月-29日)</t>
+(25年-05月-30日)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -33151,7 +33175,7 @@
           <t>D | 936呎 (3房)
 $2736万
 $29,231/呎
-(25年-10月-15日)</t>
+(25年-10月-16日)</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
@@ -33159,7 +33183,7 @@
           <t>E | 469呎 (2房)
 $1104万
 $23,529/呎
-(25年-05月-14日)</t>
+(25年-05月-15日)</t>
         </is>
       </c>
     </row>
@@ -33174,7 +33198,7 @@
           <t>A | 957呎 (3房)
 $2780万
 $29,050/呎
-(25年-12月-04日)</t>
+(25年-12月-05日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -33182,7 +33206,7 @@
           <t>B | 525呎 (2房)
 $1283万
 $24,430/呎
-(25年-05月-14日)</t>
+(25年-05月-15日)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -33190,7 +33214,7 @@
           <t>C | 522呎 (2房)
 $1374万
 $26,327/呎
-(25年-05月-28日)</t>
+(25年-05月-29日)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -33198,7 +33222,7 @@
           <t>D | 936呎 (3房)
 $2689万
 $28,731/呎
-(25年-11月-24日)</t>
+(25年-11月-25日)</t>
         </is>
       </c>
       <c r="F11" s="22" t="inlineStr">
@@ -33206,7 +33230,7 @@
           <t>E | 469呎 (2房)
 $1247万
 $26,587/呎
-(24年-04月-17日)</t>
+(24年-04月-18日)</t>
         </is>
       </c>
     </row>
@@ -33221,7 +33245,7 @@
           <t>A | 957呎 (3房)
 $3030万
 $31,659/呎
-(23年-06月-14日)</t>
+(23年-06月-15日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -33229,7 +33253,7 @@
           <t>B | 525呎 (2房)
 $1587万
 $30,232/呎
-(23年-12月-07日)</t>
+(23年-12月-08日)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -33237,7 +33261,7 @@
           <t>C | 522呎 (2房)
 $1363万
 $26,118/呎
-(25年-05月-29日)</t>
+(25年-05月-30日)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -33245,7 +33269,7 @@
           <t>D | 936呎 (3房)
 $2642万
 $28,230/呎
-(25年-11月-16日)</t>
+(25年-11月-17日)</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
@@ -33253,7 +33277,7 @@
           <t>E | 469呎 (2房)
 $1268万
 $27,042/呎
-(23年-06月-11日)</t>
+(23年-06月-12日)</t>
         </is>
       </c>
     </row>
@@ -33268,7 +33292,7 @@
           <t>A | 957呎 (3房)
 $2909万
 $30,397/呎
-(23年-06月-29日)</t>
+(23年-06月-30日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -33276,7 +33300,7 @@
           <t>B | 525呎 (2房)
 $1247万
 $23,755/呎
-(25年-05月-07日)</t>
+(25年-05月-08日)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -33284,7 +33308,7 @@
           <t>C | 522呎 (2房)
 $1240万
 $23,752/呎
-(25年-05月-12日)</t>
+(25年-05月-13日)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -33292,7 +33316,7 @@
           <t>D | 936呎 (3房)
 $2595万
 $27,729/呎
-(25年-10月-23日)</t>
+(25年-10月-24日)</t>
         </is>
       </c>
       <c r="F13" s="22" t="inlineStr">
@@ -33300,7 +33324,7 @@
           <t>E | 469呎 (2房)
 $1090万
 $23,238/呎
-(25年-06月-05日)</t>
+(25年-06月-06日)</t>
         </is>
       </c>
     </row>
@@ -33315,10 +33339,57 @@
           <t>A | 957呎 (3房)
 $2994万
 $31,283/呎
-(23年-07月-24日)</t>
+(23年-07月-25日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>B | 525呎 (2房)
+$1237万
+$23,566/呎
+(25年-05月-13日)</t>
+        </is>
+      </c>
+      <c r="D14" s="22" t="inlineStr">
+        <is>
+          <t>C | 522呎 (2房)
+$1491万
+$28,563/呎
+(23年-09月-25日)</t>
+        </is>
+      </c>
+      <c r="E14" s="22" t="inlineStr">
+        <is>
+          <t>D | 937呎 (3房)
+$2549万
+$27,200/呎
+(25年-07月-24日)</t>
+        </is>
+      </c>
+      <c r="F14" s="22" t="inlineStr">
+        <is>
+          <t>E | 469呎 (2房)
+$1253万
+$26,721/呎
+(23年-06月-20日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>A | 957呎 (3房)
+$2589万
+$27,050/呎
+(25年-11月-26日)</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
         <is>
           <t>B | 525呎 (2房)
 $1237万
@@ -33326,59 +33397,12 @@
 (25年-05月-12日)</t>
         </is>
       </c>
-      <c r="D14" s="22" t="inlineStr">
-        <is>
-          <t>C | 522呎 (2房)
-$1491万
-$28,563/呎
-(23年-09月-24日)</t>
-        </is>
-      </c>
-      <c r="E14" s="22" t="inlineStr">
-        <is>
-          <t>D | 937呎 (3房)
-$2549万
-$27,200/呎
-(25年-07月-23日)</t>
-        </is>
-      </c>
-      <c r="F14" s="22" t="inlineStr">
-        <is>
-          <t>E | 469呎 (2房)
-$1253万
-$26,721/呎
-(23年-06月-19日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="58" customHeight="1">
-      <c r="A15" s="19" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="B15" s="22" t="inlineStr">
-        <is>
-          <t>A | 957呎 (3房)
-$2589万
-$27,050/呎
-(25年-11月-25日)</t>
-        </is>
-      </c>
-      <c r="C15" s="22" t="inlineStr">
-        <is>
-          <t>B | 525呎 (2房)
-$1237万
-$23,566/呎
-(25年-05月-11日)</t>
-        </is>
-      </c>
       <c r="D15" s="22" t="inlineStr">
         <is>
           <t>C | 522呎 (2房)
 $1230万
 $23,565/呎
-(25年-05月-01日)</t>
+(25年-05月-02日)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -33386,7 +33410,7 @@
           <t>D | 937呎 (3房)
 $2502万
 $26,700/呎
-(25年-10月-27日)</t>
+(25年-10月-28日)</t>
         </is>
       </c>
       <c r="F15" s="22" t="inlineStr">
@@ -33394,7 +33418,7 @@
           <t>E | 469呎 (2房)
 $1232万
 $26,265/呎
-(23年-06月-08日)</t>
+(23年-06月-09日)</t>
         </is>
       </c>
     </row>
@@ -33409,7 +33433,7 @@
           <t>A | 957呎 (3房)
 $2560万
 $26,750/呎
-(25年-11月-25日)</t>
+(25年-11月-26日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -33417,7 +33441,7 @@
           <t>B | 525呎 (2房)
 $1225万
 $23,333/呎
-(25年-05月-12日)</t>
+(25年-05月-13日)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -33425,7 +33449,7 @@
           <t>C | 522呎 (2房)
 $1218万
 $23,332/呎
-(25年-05月-05日)</t>
+(25年-05月-06日)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -33433,7 +33457,7 @@
           <t>D | 936呎 (3房)
 $2474万
 $26,427/呎
-(25年-10月-23日)</t>
+(25年-10月-24日)</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
@@ -33441,7 +33465,7 @@
           <t>E | 469呎 (2房)
 $1203万
 $25,656/呎
-(23年-06月-12日)</t>
+(23年-06月-13日)</t>
         </is>
       </c>
     </row>
@@ -33456,7 +33480,7 @@
           <t>A | 957呎 (3房)
 $2874万
 $30,030/呎
-(23年-10月-08日)</t>
+(23年-10月-09日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -33464,7 +33488,7 @@
           <t>B | 525呎 (2房)
 $1219万
 $23,216/呎
-(25年-05月-07日)</t>
+(25年-05月-08日)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -33472,7 +33496,7 @@
           <t>C | 522呎 (2房)
 $1212万
 $23,214/呎
-(25年-05月-13日)</t>
+(25年-05月-14日)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -33480,7 +33504,7 @@
           <t>D | 936呎 (3房)
 $2441万
 $26,078/呎
-(25年-09月-08日)</t>
+(25年-09月-09日)</t>
         </is>
       </c>
       <c r="F17" s="22" t="inlineStr">
@@ -33488,7 +33512,7 @@
           <t>E | 469呎 (2房)
 $1242万
 $26,481/呎
-(23年-06月-11日)</t>
+(23年-06月-12日)</t>
         </is>
       </c>
     </row>
@@ -33503,7 +33527,7 @@
           <t>A | 957呎 (3房)
 $2923万
 $30,544/呎
-(23年-06月-14日)</t>
+(23年-06月-15日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -33511,7 +33535,7 @@
           <t>B | 525呎 (2房)
 $1213万
 $23,101/呎
-(25年-05月-15日)</t>
+(25年-05月-16日)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -33519,7 +33543,7 @@
           <t>C | 522呎 (2房)
 $1206万
 $23,098/呎
-(25年-05月-11日)</t>
+(25年-05月-12日)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -33527,7 +33551,7 @@
           <t>D | 936呎 (3房)
 $2417万
 $25,827/呎
-(25年-09月-03日)</t>
+(25年-09月-04日)</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
@@ -33535,7 +33559,7 @@
           <t>E | 469呎 (2房)
 $1238万
 $26,402/呎
-(23年-06月-18日)</t>
+(23年-06月-19日)</t>
         </is>
       </c>
     </row>
@@ -33550,7 +33574,7 @@
           <t>A | 957呎 (3房)
 $2474万
 $25,850/呎
-(25年-11月-19日)</t>
+(25年-11月-20日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -33558,7 +33582,7 @@
           <t>B | 525呎 (2房)
 $1250万
 $23,806/呎
-(25年-05月-07日)</t>
+(25年-05月-08日)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -33566,7 +33590,7 @@
           <t>C | 522呎 (2房)
 $1257万
 $24,079/呎
-(25年-05月-14日)</t>
+(25年-05月-15日)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -33574,7 +33598,7 @@
           <t>D | 936呎 (3房)
 $2389万
 $25,527/呎
-(25年-09月-15日)</t>
+(25年-09月-16日)</t>
         </is>
       </c>
       <c r="F19" s="22" t="inlineStr">
@@ -33582,7 +33606,7 @@
           <t>E | 469呎 (2房)
 $1231万
 $26,244/呎
-(23年-06月-14日)</t>
+(23年-06月-15日)</t>
         </is>
       </c>
     </row>
@@ -33597,7 +33621,7 @@
           <t>A | 957呎 (3房)
 $2445万
 $25,550/呎
-(25年-11月-06日)</t>
+(25年-11月-07日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -33605,7 +33629,7 @@
           <t>B | 525呎 (2房)
 $1490万
 $28,383/呎
-(23年-06月-12日)</t>
+(23年-06月-13日)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -33613,7 +33637,7 @@
           <t>C | 522呎 (2房)
 $1230万
 $23,562/呎
-(25年-05月-29日)</t>
+(25年-05月-30日)</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
@@ -33621,7 +33645,7 @@
           <t>D | 937呎 (3房)
 $2361万
 $25,200/呎
-(25年-09月-14日)</t>
+(25年-09月-15日)</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
@@ -33629,7 +33653,7 @@
           <t>E | 469呎 (2房)
 $1224万
 $26,088/呎
-(23年-06月-12日)</t>
+(23年-06月-13日)</t>
         </is>
       </c>
     </row>
@@ -33644,7 +33668,7 @@
           <t>A | 957呎 (3房)
 $2383万
 $24,900/呎
-(25年-11月-30日)</t>
+(25年-12月-01日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -33652,7 +33676,7 @@
           <t>B | 525呎 (2房)
 $1177万
 $22,422/呎
-(25年-05月-15日)</t>
+(25年-05月-16日)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -33660,7 +33684,7 @@
           <t>C | 522呎 (2房)
 $1170万
 $22,421/呎
-(25年-05月-20日)</t>
+(25年-05月-21日)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -33668,7 +33692,7 @@
           <t>D | 937呎 (3房)
 $2314万
 $24,700/呎
-(25年-10月-13日)</t>
+(25年-10月-14日)</t>
         </is>
       </c>
       <c r="F21" s="22" t="inlineStr">
@@ -33676,7 +33700,7 @@
           <t>E | 469呎 (2房)
 $1196万
 $25,491/呎
-(23年-06月-11日)</t>
+(23年-06月-12日)</t>
         </is>
       </c>
     </row>
@@ -33691,7 +33715,7 @@
           <t>A | 957呎 (3房)
 $2378万
 $24,850/呎
-(25年-12月-17日)</t>
+(25年-12月-18日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -33699,7 +33723,7 @@
           <t>B | 525呎 (2房)
 $1201万
 $22,880/呎
-(25年-05月-21日)</t>
+(25年-05月-22日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -33707,7 +33731,7 @@
           <t>C | 522呎 (2房)
 $1153万
 $22,088/呎
-(25年-05月-21日)</t>
+(25年-05月-22日)</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -33715,7 +33739,7 @@
           <t>D | 937呎 (3房)
 $2268万
 $24,200/呎
-(25年-09月-25日)</t>
+(25年-09月-26日)</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
@@ -33723,7 +33747,7 @@
           <t>E | 469呎 (2房)
 $1209万
 $25,779/呎
-(23年-06月-11日)</t>
+(23年-06月-12日)</t>
         </is>
       </c>
     </row>
@@ -33738,7 +33762,7 @@
           <t>A | 957呎 (3房)
 $2349万
 $24,550/呎
-(25年-12月-22日)</t>
+(25年-12月-23日)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -33746,7 +33770,7 @@
           <t>B | 525呎 (2房)
 $1143万
 $21,765/呎
-(25年-05月-08日)</t>
+(25年-05月-09日)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -33754,7 +33778,7 @@
           <t>C | 522呎 (2房)
 $1136万
 $21,761/呎
-(25年-05月-08日)</t>
+(25年-05月-09日)</t>
         </is>
       </c>
       <c r="E23" s="22" t="inlineStr">
@@ -33762,7 +33786,7 @@
           <t>D | 936呎 (3房)
 $2239万
 $23,926/呎
-(25年-11月-03日)</t>
+(25年-11月-04日)</t>
         </is>
       </c>
       <c r="F23" s="22" t="inlineStr">
@@ -33770,7 +33794,7 @@
           <t>E | 469呎 (2房)
 $1188万
 $25,339/呎
-(23年-06月-14日)</t>
+(23年-06月-15日)</t>
         </is>
       </c>
     </row>
@@ -33785,7 +33809,7 @@
           <t>A | 957呎 (3房)
 $2278万
 $23,800/呎
-(25年-11月-23日)</t>
+(25年-11月-24日)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -33793,7 +33817,7 @@
           <t>B | 525呎 (2房)
 $1421万
 $27,074/呎
-(23年-06月-18日)</t>
+(23年-06月-19日)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -33801,7 +33825,7 @@
           <t>C | 522呎 (2房)
 $1404万
 $26,906/呎
-(23年-06月-18日)</t>
+(23年-06月-19日)</t>
         </is>
       </c>
       <c r="E24" s="22" t="inlineStr">
@@ -33809,7 +33833,7 @@
           <t>D | 936呎 (3房)
 $2253万
 $24,076/呎
-(26年-01月-28日)</t>
+(26年-01月-29日)</t>
         </is>
       </c>
       <c r="F24" s="22" t="inlineStr">
@@ -33817,7 +33841,7 @@
           <t>E | 469呎 (2房)
 $1195万
 $25,473/呎
-(23年-06月-13日)</t>
+(23年-06月-14日)</t>
         </is>
       </c>
     </row>
@@ -33832,7 +33856,7 @@
           <t>A | 957呎 (3房)
 $2292万
 $23,950/呎
-(26年-01月-08日)</t>
+(26年-01月-09日)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -33840,7 +33864,7 @@
           <t>B | 525呎 (2房)
 $1400万
 $26,675/呎
-(23年-06月-12日)</t>
+(23年-06月-13日)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -33848,7 +33872,7 @@
           <t>C | 522呎 (2房)
 $1384万
 $26,508/呎
-(23年-06月-13日)</t>
+(23年-06月-14日)</t>
         </is>
       </c>
       <c r="E25" s="22" t="inlineStr">
@@ -33856,7 +33880,7 @@
           <t>D | 936呎 (3房)
 $2183万
 $23,325/呎
-(25年-11月-25日)</t>
+(25年-11月-26日)</t>
         </is>
       </c>
       <c r="F25" s="22" t="inlineStr">
@@ -33864,7 +33888,7 @@
           <t>E | 469呎 (2房)
 $1131万
 $24,123/呎
-(23年-06月-12日)</t>
+(23年-06月-13日)</t>
         </is>
       </c>
     </row>
@@ -33879,7 +33903,7 @@
           <t>A | 957呎 (3房)
 $2263万
 $23,650/呎
-(26年-03月-18日)</t>
+(26年-03月-19日)</t>
         </is>
       </c>
       <c r="C26" s="22" t="inlineStr">
@@ -33887,7 +33911,7 @@
           <t>B | 525呎 (2房)
 $1356万
 $25,831/呎
-(23年-06月-19日)</t>
+(23年-06月-20日)</t>
         </is>
       </c>
       <c r="D26" s="22" t="inlineStr">
@@ -33895,7 +33919,7 @@
           <t>C | 522呎 (2房)
 $1172万
 $22,452/呎
-(25年-06月-09日)</t>
+(25年-06月-10日)</t>
         </is>
       </c>
       <c r="E26" s="22" t="inlineStr">
@@ -33903,7 +33927,7 @@
           <t>D | 936呎 (3房)
 $2155万
 $23,025/呎
-(25年-12月-03日)</t>
+(25年-12月-04日)</t>
         </is>
       </c>
       <c r="F26" s="22" t="inlineStr">
@@ -33911,7 +33935,7 @@
           <t>E | 469呎 (2房)
 $1109万
 $23,649/呎
-(23年-06月-13日)</t>
+(23年-06月-14日)</t>
         </is>
       </c>
     </row>
@@ -33926,7 +33950,7 @@
           <t>A | 957呎 (3房)
 $2235万
 $23,350/呎
-(26年-03月-22日)</t>
+(26年-03月-23日)</t>
         </is>
       </c>
       <c r="C27" s="22" t="inlineStr">
@@ -33934,7 +33958,7 @@
           <t>B | 525呎 (2房)
 $1045万
 $19,909/呎
-(25年-05月-11日)</t>
+(25年-05月-12日)</t>
         </is>
       </c>
       <c r="D27" s="22" t="inlineStr">
@@ -33942,7 +33966,7 @@
           <t>C | 522呎 (2房)
 $1162万
 $22,258/呎
-(25年-05月-28日)</t>
+(25年-05月-29日)</t>
         </is>
       </c>
       <c r="E27" s="22" t="inlineStr">
@@ -33950,7 +33974,7 @@
           <t>D | 936呎 (3房)
 $2169万
 $23,175/呎
-(25年-12月-23日)</t>
+(25年-12月-24日)</t>
         </is>
       </c>
       <c r="F27" s="22" t="inlineStr">
@@ -33958,7 +33982,7 @@
           <t>E | 469呎 (2房)
 $1087万
 $23,186/呎
-(23年-06月-11日)</t>
+(23年-06月-12日)</t>
         </is>
       </c>
     </row>
@@ -33973,7 +33997,7 @@
           <t>A | 957呎 (3房)
 $2220万
 $23,200/呎
-(26年-04月-09日)</t>
+(26年-04月-10日)</t>
         </is>
       </c>
       <c r="C28" s="22" t="inlineStr">
@@ -33981,7 +34005,7 @@
           <t>B | 525呎 (2房)
 $1275万
 $24,279/呎
-(23年-07月-30日)</t>
+(23年-07月-31日)</t>
         </is>
       </c>
       <c r="D28" s="22" t="inlineStr">
@@ -33989,7 +34013,7 @@
           <t>C | 522呎 (2房)
 $1304万
 $24,979/呎
-(23年-06月-29日)</t>
+(23年-06月-30日)</t>
         </is>
       </c>
       <c r="E28" s="22" t="inlineStr">
@@ -33997,7 +34021,7 @@
           <t>D | 936呎 (3房)
 $2174万
 $23,225/呎
-(26年-04月-08日)</t>
+(26年-04月-09日)</t>
         </is>
       </c>
       <c r="F28" s="22" t="inlineStr">
@@ -34005,7 +34029,7 @@
           <t>E | 469呎 (2房)
 $1085万
 $23,132/呎
-(23年-06月-27日)</t>
+(23年-06月-28日)</t>
         </is>
       </c>
     </row>
@@ -34020,7 +34044,7 @@
           <t>A | 914呎 (3房)
 $2422万
 $26,500/呎
-(26年-04月-01日)</t>
+(26年-04月-02日)</t>
         </is>
       </c>
       <c r="C29" s="22" t="inlineStr">
@@ -34028,7 +34052,7 @@
           <t>B | 482呎 (2房)
 $1170万
 $24,281/呎
-(25年-10月-27日)</t>
+(25年-10月-28日)</t>
         </is>
       </c>
       <c r="D29" s="22" t="inlineStr">
@@ -34036,7 +34060,7 @@
           <t>C | 479呎 (2房)
 $1186万
 $24,768/呎
-(25年-05月-26日)</t>
+(25年-05月-27日)</t>
         </is>
       </c>
       <c r="E29" s="22" t="inlineStr">
@@ -34044,7 +34068,7 @@
           <t>D | 894呎 (3房)
 $2771万
 $31,000/呎
-(26年-01月-04日)</t>
+(26年-01月-05日)</t>
         </is>
       </c>
       <c r="F29" s="22" t="inlineStr">
@@ -34052,7 +34076,7 @@
           <t>E | 431呎 (2房)
 $1183万
 $27,437/呎
-(23年-06月-11日)</t>
+(23年-06月-12日)</t>
         </is>
       </c>
     </row>

--- a/files/九龙-何文田-瑜一．天海.xlsx
+++ b/files/九龙-何文田-瑜一．天海.xlsx
@@ -10123,38 +10123,30 @@
       </c>
       <c r="F151" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H151" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I151" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="H151" s="5" t="n">
+        <v>27648000</v>
+      </c>
+      <c r="I151" s="5" t="n">
+        <v>28800</v>
       </c>
       <c r="J151" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K151" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L151" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K151" s="5" t="n">
+        <v>27648000</v>
+      </c>
+      <c r="L151" s="5" t="n">
+        <v>28800</v>
       </c>
       <c r="M151" s="3" t="inlineStr">
         <is>
@@ -10163,7 +10155,7 @@
       </c>
       <c r="N151" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -17065,38 +17057,30 @@
       </c>
       <c r="F260" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G260" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H260" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I260" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="H260" s="5" t="n">
+        <v>19039000</v>
+      </c>
+      <c r="I260" s="5" t="n">
+        <v>32106</v>
       </c>
       <c r="J260" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K260" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L260" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K260" s="5" t="n">
+        <v>19039000</v>
+      </c>
+      <c r="L260" s="5" t="n">
+        <v>32106</v>
       </c>
       <c r="M260" s="3" t="inlineStr">
         <is>
@@ -17105,7 +17089,7 @@
       </c>
       <c r="N260" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -21289,38 +21273,30 @@
       </c>
       <c r="F324" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G324" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H324" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I324" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="H324" s="5" t="n">
+        <v>32010000</v>
+      </c>
+      <c r="I324" s="5" t="n">
+        <v>36007</v>
       </c>
       <c r="J324" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K324" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L324" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K324" s="5" t="n">
+        <v>32010000</v>
+      </c>
+      <c r="L324" s="5" t="n">
+        <v>36007</v>
       </c>
       <c r="M324" s="3" t="inlineStr">
         <is>
@@ -21329,7 +21305,7 @@
       </c>
       <c r="N324" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -30386,7 +30362,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -30396,7 +30372,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>124</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -30871,12 +30847,12 @@
           <t>19</t>
         </is>
       </c>
-      <c r="B14" s="20" t="inlineStr">
+      <c r="B14" s="22" t="inlineStr">
         <is>
           <t>A | 960呎 (3房)
-招标单位
--
-(在售)</t>
+$2765万
+$28,800/呎
+(26年-07月-31日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -31691,7 +31667,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -31701,7 +31677,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>42</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -32115,7 +32091,48 @@
 (26年-06月-05日)</t>
         </is>
       </c>
-      <c r="D14" s="20" t="inlineStr">
+      <c r="D14" s="22" t="inlineStr">
+        <is>
+          <t>C | 593呎 (2房)
+$1904万
+$32,106/呎
+(26年-07月-31日)</t>
+        </is>
+      </c>
+      <c r="E14" s="23" t="inlineStr">
+        <is>
+          <t>D | 992呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F14" s="21" t="inlineStr"/>
+      <c r="G14" s="21" t="inlineStr"/>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>A | 997呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>B | 597呎 (2房)
+$1928万
+$32,295/呎
+(26年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="D15" s="20" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -32123,7 +32140,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E14" s="23" t="inlineStr">
+      <c r="E15" s="23" t="inlineStr">
         <is>
           <t>D | 992呎 (3房)
 -
@@ -32131,16 +32148,303 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F14" s="21" t="inlineStr"/>
-      <c r="G14" s="21" t="inlineStr"/>
-    </row>
-    <row r="15" ht="58" customHeight="1">
-      <c r="A15" s="19" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="B15" s="20" t="inlineStr">
+      <c r="F15" s="21" t="inlineStr"/>
+      <c r="G15" s="21" t="inlineStr"/>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>A | 997呎 (3房)
+$3210万
+$32,201/呎
+(26年-05月-20日)</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>B | 597呎 (2房)
+$1883万
+$31,536/呎
+(26年-05月-06日)</t>
+        </is>
+      </c>
+      <c r="D16" s="25" t="inlineStr">
+        <is>
+          <t>C | 593呎 (2房)
+$2215万
+$37,352/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E16" s="23" t="inlineStr">
+        <is>
+          <t>D | 992呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F16" s="21" t="inlineStr"/>
+      <c r="G16" s="21" t="inlineStr"/>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>A | 997呎 (3房)
+$3170万
+$31,800/呎
+(26年-05月-18日)</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>B | 597呎 (2房)
+$1871万
+$31,347/呎
+(26年-05月-05日)</t>
+        </is>
+      </c>
+      <c r="D17" s="25" t="inlineStr">
+        <is>
+          <t>C | 593呎 (2房)
+$2202万
+$37,130/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E17" s="23" t="inlineStr">
+        <is>
+          <t>D | 992呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F17" s="21" t="inlineStr"/>
+      <c r="G17" s="21" t="inlineStr"/>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>A | 997呎 (3房)
+$3121万
+$31,300/呎
+(26年-05月-26日)</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>B | 597呎 (2房)
+$1876万
+$31,419/呎
+(24年-04月-11日)</t>
+        </is>
+      </c>
+      <c r="D18" s="20" t="inlineStr">
+        <is>
+          <t>C | 593呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E18" s="23" t="inlineStr">
+        <is>
+          <t>D | 992呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F18" s="21" t="inlineStr"/>
+      <c r="G18" s="21" t="inlineStr"/>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>A | 997呎 (3房)
+$3071万
+$30,800/呎
+(26年-06月-05日)</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>B | 597呎 (2房)
+$1851万
+$31,005/呎
+(26年-05月-06日)</t>
+        </is>
+      </c>
+      <c r="D19" s="20" t="inlineStr">
+        <is>
+          <t>C | 593呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E19" s="23" t="inlineStr">
+        <is>
+          <t>D | 992呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F19" s="21" t="inlineStr"/>
+      <c r="G19" s="21" t="inlineStr"/>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>A | 997呎 (3房)
+$3021万
+$30,301/呎
+(26年-07月-28日)</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>B | 597呎 (2房)
+$1923万
+$32,205/呎
+(23年-06月-12日)</t>
+        </is>
+      </c>
+      <c r="D20" s="22" t="inlineStr">
+        <is>
+          <t>C | 593呎 (2房)
+$1907万
+$32,156/呎
+(23年-06月-12日)</t>
+        </is>
+      </c>
+      <c r="E20" s="23" t="inlineStr">
+        <is>
+          <t>D | 992呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F20" s="21" t="inlineStr"/>
+      <c r="G20" s="21" t="inlineStr"/>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>A | 997呎 (3房)
+$2971万
+$29,800/呎
+(26年-07月-20日)</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="inlineStr">
+        <is>
+          <t>B | 597呎 (2房)
+$1869万
+$31,310/呎
+(26年-06月-30日)</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="inlineStr">
+        <is>
+          <t>C | 593呎 (2房)
+$1833万
+$30,905/呎
+(23年-07月-04日)</t>
+        </is>
+      </c>
+      <c r="E21" s="23" t="inlineStr">
+        <is>
+          <t>D | 992呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F21" s="21" t="inlineStr"/>
+      <c r="G21" s="21" t="inlineStr"/>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>A | 997呎 (3房)
+$2921万
+$29,301/呎
+(26年-06月-26日)</t>
+        </is>
+      </c>
+      <c r="C22" s="20" t="inlineStr">
+        <is>
+          <t>B | 597呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D22" s="22" t="inlineStr">
+        <is>
+          <t>C | 593呎 (2房)
+$1836万
+$30,960/呎
+(23年-11月-13日)</t>
+        </is>
+      </c>
+      <c r="E22" s="23" t="inlineStr">
+        <is>
+          <t>D | 992呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F22" s="21" t="inlineStr"/>
+      <c r="G22" s="21" t="inlineStr"/>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
         <is>
           <t>A | 997呎 (3房)
 招标单位
@@ -32148,15 +32452,56 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C15" s="22" t="inlineStr">
+      <c r="C23" s="22" t="inlineStr">
         <is>
           <t>B | 597呎 (2房)
-$1928万
-$32,295/呎
-(26年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="D15" s="20" t="inlineStr">
+$1765万
+$29,564/呎
+(26年-06月-02日)</t>
+        </is>
+      </c>
+      <c r="D23" s="22" t="inlineStr">
+        <is>
+          <t>C | 593呎 (2房)
+$1786万
+$30,117/呎
+(24年-02月-07日)</t>
+        </is>
+      </c>
+      <c r="E23" s="23" t="inlineStr">
+        <is>
+          <t>D | 992呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F23" s="21" t="inlineStr"/>
+      <c r="G23" s="21" t="inlineStr"/>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
+        <is>
+          <t>A | 997呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C24" s="22" t="inlineStr">
+        <is>
+          <t>B | 597呎 (2房)
+$1789万
+$29,964/呎
+(23年-06月-27日)</t>
+        </is>
+      </c>
+      <c r="D24" s="20" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -32164,7 +32509,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E15" s="23" t="inlineStr">
+      <c r="E24" s="23" t="inlineStr">
         <is>
           <t>D | 992呎 (3房)
 -
@@ -32172,40 +32517,40 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F15" s="21" t="inlineStr"/>
-      <c r="G15" s="21" t="inlineStr"/>
-    </row>
-    <row r="16" ht="58" customHeight="1">
-      <c r="A16" s="19" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="B16" s="22" t="inlineStr">
+      <c r="F24" s="21" t="inlineStr"/>
+      <c r="G24" s="21" t="inlineStr"/>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
         <is>
           <t>A | 997呎 (3房)
-$3210万
-$32,201/呎
-(26年-05月-20日)</t>
-        </is>
-      </c>
-      <c r="C16" s="22" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C25" s="22" t="inlineStr">
         <is>
           <t>B | 597呎 (2房)
-$1883万
-$31,536/呎
-(26年-05月-06日)</t>
-        </is>
-      </c>
-      <c r="D16" s="25" t="inlineStr">
+$1680万
+$28,141/呎
+(26年-05月-22日)</t>
+        </is>
+      </c>
+      <c r="D25" s="22" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
-$2215万
-$37,352/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E16" s="23" t="inlineStr">
+$1723万
+$29,047/呎
+(23年-06月-15日)</t>
+        </is>
+      </c>
+      <c r="E25" s="23" t="inlineStr">
         <is>
           <t>D | 992呎 (3房)
 -
@@ -32213,40 +32558,40 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F16" s="21" t="inlineStr"/>
-      <c r="G16" s="21" t="inlineStr"/>
-    </row>
-    <row r="17" ht="58" customHeight="1">
-      <c r="A17" s="19" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B17" s="22" t="inlineStr">
+      <c r="F25" s="21" t="inlineStr"/>
+      <c r="G25" s="21" t="inlineStr"/>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
         <is>
           <t>A | 997呎 (3房)
-$3170万
-$31,800/呎
-(26年-05月-18日)</t>
-        </is>
-      </c>
-      <c r="C17" s="22" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C26" s="22" t="inlineStr">
         <is>
           <t>B | 597呎 (2房)
-$1871万
-$31,347/呎
-(26年-05月-05日)</t>
-        </is>
-      </c>
-      <c r="D17" s="25" t="inlineStr">
+$1657万
+$27,762/呎
+(23年-06月-14日)</t>
+        </is>
+      </c>
+      <c r="D26" s="20" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
-$2202万
-$37,130/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E17" s="23" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E26" s="23" t="inlineStr">
         <is>
           <t>D | 992呎 (3房)
 -
@@ -32254,40 +32599,40 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F17" s="21" t="inlineStr"/>
-      <c r="G17" s="21" t="inlineStr"/>
-    </row>
-    <row r="18" ht="58" customHeight="1">
-      <c r="A18" s="19" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="B18" s="22" t="inlineStr">
+      <c r="F26" s="21" t="inlineStr"/>
+      <c r="G26" s="21" t="inlineStr"/>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="inlineStr">
         <is>
           <t>A | 997呎 (3房)
-$3121万
-$31,300/呎
-(26年-05月-26日)</t>
-        </is>
-      </c>
-      <c r="C18" s="22" t="inlineStr">
-        <is>
-          <t>B | 597呎 (2房)
-$1876万
-$31,419/呎
-(24年-04月-11日)</t>
-        </is>
-      </c>
-      <c r="D18" s="20" t="inlineStr">
-        <is>
-          <t>C | 593呎 (2房)
 招标单位
 -
 (在售)</t>
         </is>
       </c>
-      <c r="E18" s="23" t="inlineStr">
+      <c r="C27" s="22" t="inlineStr">
+        <is>
+          <t>B | 597呎 (2房)
+$1581万
+$26,487/呎
+(24年-03月-22日)</t>
+        </is>
+      </c>
+      <c r="D27" s="22" t="inlineStr">
+        <is>
+          <t>C | 593呎 (2房)
+$1624万
+$27,381/呎
+(23年-06月-13日)</t>
+        </is>
+      </c>
+      <c r="E27" s="23" t="inlineStr">
         <is>
           <t>D | 992呎 (3房)
 -
@@ -32295,40 +32640,40 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F18" s="21" t="inlineStr"/>
-      <c r="G18" s="21" t="inlineStr"/>
-    </row>
-    <row r="19" ht="58" customHeight="1">
-      <c r="A19" s="19" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B19" s="22" t="inlineStr">
+      <c r="F27" s="21" t="inlineStr"/>
+      <c r="G27" s="21" t="inlineStr"/>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
         <is>
           <t>A | 997呎 (3房)
-$3071万
-$30,800/呎
-(26年-06月-05日)</t>
-        </is>
-      </c>
-      <c r="C19" s="22" t="inlineStr">
-        <is>
-          <t>B | 597呎 (2房)
-$1851万
-$31,005/呎
-(26年-05月-06日)</t>
-        </is>
-      </c>
-      <c r="D19" s="20" t="inlineStr">
-        <is>
-          <t>C | 593呎 (2房)
 招标单位
 -
 (在售)</t>
         </is>
       </c>
-      <c r="E19" s="23" t="inlineStr">
+      <c r="C28" s="22" t="inlineStr">
+        <is>
+          <t>B | 597呎 (2房)
+$1589万
+$26,622/呎
+(23年-07月-04日)</t>
+        </is>
+      </c>
+      <c r="D28" s="22" t="inlineStr">
+        <is>
+          <t>C | 593呎 (2房)
+$1576万
+$26,584/呎
+(23年-06月-13日)</t>
+        </is>
+      </c>
+      <c r="E28" s="23" t="inlineStr">
         <is>
           <t>D | 992呎 (3房)
 -
@@ -32336,375 +32681,6 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F19" s="21" t="inlineStr"/>
-      <c r="G19" s="21" t="inlineStr"/>
-    </row>
-    <row r="20" ht="58" customHeight="1">
-      <c r="A20" s="19" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B20" s="22" t="inlineStr">
-        <is>
-          <t>A | 997呎 (3房)
-$3021万
-$30,301/呎
-(26年-07月-28日)</t>
-        </is>
-      </c>
-      <c r="C20" s="22" t="inlineStr">
-        <is>
-          <t>B | 597呎 (2房)
-$1923万
-$32,205/呎
-(23年-06月-12日)</t>
-        </is>
-      </c>
-      <c r="D20" s="22" t="inlineStr">
-        <is>
-          <t>C | 593呎 (2房)
-$1907万
-$32,156/呎
-(23年-06月-12日)</t>
-        </is>
-      </c>
-      <c r="E20" s="23" t="inlineStr">
-        <is>
-          <t>D | 992呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F20" s="21" t="inlineStr"/>
-      <c r="G20" s="21" t="inlineStr"/>
-    </row>
-    <row r="21" ht="58" customHeight="1">
-      <c r="A21" s="19" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B21" s="22" t="inlineStr">
-        <is>
-          <t>A | 997呎 (3房)
-$2971万
-$29,800/呎
-(26年-07月-20日)</t>
-        </is>
-      </c>
-      <c r="C21" s="22" t="inlineStr">
-        <is>
-          <t>B | 597呎 (2房)
-$1869万
-$31,310/呎
-(26年-06月-30日)</t>
-        </is>
-      </c>
-      <c r="D21" s="22" t="inlineStr">
-        <is>
-          <t>C | 593呎 (2房)
-$1833万
-$30,905/呎
-(23年-07月-04日)</t>
-        </is>
-      </c>
-      <c r="E21" s="23" t="inlineStr">
-        <is>
-          <t>D | 992呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F21" s="21" t="inlineStr"/>
-      <c r="G21" s="21" t="inlineStr"/>
-    </row>
-    <row r="22" ht="58" customHeight="1">
-      <c r="A22" s="19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B22" s="22" t="inlineStr">
-        <is>
-          <t>A | 997呎 (3房)
-$2921万
-$29,301/呎
-(26年-06月-26日)</t>
-        </is>
-      </c>
-      <c r="C22" s="20" t="inlineStr">
-        <is>
-          <t>B | 597呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D22" s="22" t="inlineStr">
-        <is>
-          <t>C | 593呎 (2房)
-$1836万
-$30,960/呎
-(23年-11月-13日)</t>
-        </is>
-      </c>
-      <c r="E22" s="23" t="inlineStr">
-        <is>
-          <t>D | 992呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F22" s="21" t="inlineStr"/>
-      <c r="G22" s="21" t="inlineStr"/>
-    </row>
-    <row r="23" ht="58" customHeight="1">
-      <c r="A23" s="19" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B23" s="20" t="inlineStr">
-        <is>
-          <t>A | 997呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C23" s="22" t="inlineStr">
-        <is>
-          <t>B | 597呎 (2房)
-$1765万
-$29,564/呎
-(26年-06月-02日)</t>
-        </is>
-      </c>
-      <c r="D23" s="22" t="inlineStr">
-        <is>
-          <t>C | 593呎 (2房)
-$1786万
-$30,117/呎
-(24年-02月-07日)</t>
-        </is>
-      </c>
-      <c r="E23" s="23" t="inlineStr">
-        <is>
-          <t>D | 992呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F23" s="21" t="inlineStr"/>
-      <c r="G23" s="21" t="inlineStr"/>
-    </row>
-    <row r="24" ht="58" customHeight="1">
-      <c r="A24" s="19" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B24" s="20" t="inlineStr">
-        <is>
-          <t>A | 997呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C24" s="22" t="inlineStr">
-        <is>
-          <t>B | 597呎 (2房)
-$1789万
-$29,964/呎
-(23年-06月-27日)</t>
-        </is>
-      </c>
-      <c r="D24" s="20" t="inlineStr">
-        <is>
-          <t>C | 593呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="E24" s="23" t="inlineStr">
-        <is>
-          <t>D | 992呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F24" s="21" t="inlineStr"/>
-      <c r="G24" s="21" t="inlineStr"/>
-    </row>
-    <row r="25" ht="58" customHeight="1">
-      <c r="A25" s="19" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B25" s="20" t="inlineStr">
-        <is>
-          <t>A | 997呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C25" s="22" t="inlineStr">
-        <is>
-          <t>B | 597呎 (2房)
-$1680万
-$28,141/呎
-(26年-05月-22日)</t>
-        </is>
-      </c>
-      <c r="D25" s="22" t="inlineStr">
-        <is>
-          <t>C | 593呎 (2房)
-$1723万
-$29,047/呎
-(23年-06月-15日)</t>
-        </is>
-      </c>
-      <c r="E25" s="23" t="inlineStr">
-        <is>
-          <t>D | 992呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F25" s="21" t="inlineStr"/>
-      <c r="G25" s="21" t="inlineStr"/>
-    </row>
-    <row r="26" ht="58" customHeight="1">
-      <c r="A26" s="19" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B26" s="20" t="inlineStr">
-        <is>
-          <t>A | 997呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C26" s="22" t="inlineStr">
-        <is>
-          <t>B | 597呎 (2房)
-$1657万
-$27,762/呎
-(23年-06月-14日)</t>
-        </is>
-      </c>
-      <c r="D26" s="20" t="inlineStr">
-        <is>
-          <t>C | 593呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="E26" s="23" t="inlineStr">
-        <is>
-          <t>D | 992呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F26" s="21" t="inlineStr"/>
-      <c r="G26" s="21" t="inlineStr"/>
-    </row>
-    <row r="27" ht="58" customHeight="1">
-      <c r="A27" s="19" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B27" s="20" t="inlineStr">
-        <is>
-          <t>A | 997呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C27" s="22" t="inlineStr">
-        <is>
-          <t>B | 597呎 (2房)
-$1581万
-$26,487/呎
-(24年-03月-22日)</t>
-        </is>
-      </c>
-      <c r="D27" s="22" t="inlineStr">
-        <is>
-          <t>C | 593呎 (2房)
-$1624万
-$27,381/呎
-(23年-06月-13日)</t>
-        </is>
-      </c>
-      <c r="E27" s="23" t="inlineStr">
-        <is>
-          <t>D | 992呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F27" s="21" t="inlineStr"/>
-      <c r="G27" s="21" t="inlineStr"/>
-    </row>
-    <row r="28" ht="58" customHeight="1">
-      <c r="A28" s="19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B28" s="20" t="inlineStr">
-        <is>
-          <t>A | 997呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C28" s="22" t="inlineStr">
-        <is>
-          <t>B | 597呎 (2房)
-$1589万
-$26,622/呎
-(23年-07月-04日)</t>
-        </is>
-      </c>
-      <c r="D28" s="22" t="inlineStr">
-        <is>
-          <t>C | 593呎 (2房)
-$1576万
-$26,584/呎
-(23年-06月-13日)</t>
-        </is>
-      </c>
-      <c r="E28" s="23" t="inlineStr">
-        <is>
-          <t>D | 992呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
       <c r="F28" s="21" t="inlineStr"/>
       <c r="G28" s="21" t="inlineStr"/>
     </row>
@@ -32759,12 +32735,12 @@
       <c r="C30" s="21" t="inlineStr"/>
       <c r="D30" s="21" t="inlineStr"/>
       <c r="E30" s="21" t="inlineStr"/>
-      <c r="F30" s="20" t="inlineStr">
+      <c r="F30" s="22" t="inlineStr">
         <is>
           <t>MAISON D | 889呎 (3房)
-招标单位
--
-(在售)</t>
+$3201万
+$36,007/呎
+(26年-07月-31日)</t>
         </is>
       </c>
       <c r="G30" s="22" t="inlineStr">

--- a/files/九龙-何文田-瑜一．天海.xlsx
+++ b/files/九龙-何文田-瑜一．天海.xlsx
@@ -10119,7 +10119,7 @@
         </is>
       </c>
       <c r="E151" s="4" t="n">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="F151" s="3" t="inlineStr">
         <is>
@@ -10135,7 +10135,7 @@
         <v>27648000</v>
       </c>
       <c r="I151" s="5" t="n">
-        <v>28800</v>
+        <v>28830</v>
       </c>
       <c r="J151" s="3" t="inlineStr">
         <is>
@@ -10146,7 +10146,7 @@
         <v>27648000</v>
       </c>
       <c r="L151" s="5" t="n">
-        <v>28800</v>
+        <v>28830</v>
       </c>
       <c r="M151" s="3" t="inlineStr">
         <is>
@@ -16257,38 +16257,30 @@
       </c>
       <c r="F248" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G248" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H248" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I248" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="H248" s="5" t="n">
+        <v>19967000</v>
+      </c>
+      <c r="I248" s="5" t="n">
+        <v>33671</v>
       </c>
       <c r="J248" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K248" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L248" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K248" s="5" t="n">
+        <v>19967000</v>
+      </c>
+      <c r="L248" s="5" t="n">
+        <v>33671</v>
       </c>
       <c r="M248" s="3" t="inlineStr">
         <is>
@@ -16297,7 +16289,7 @@
       </c>
       <c r="N248" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -18956,7 +18948,7 @@
       </c>
       <c r="G289" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="H289" s="5" t="n">
@@ -19282,7 +19274,7 @@
       </c>
       <c r="G294" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="H294" s="5" t="n">
@@ -30849,9 +30841,9 @@
       </c>
       <c r="B14" s="22" t="inlineStr">
         <is>
-          <t>A | 960呎 (3房)
+          <t>A | 959呎 (3房)
 $2765万
-$28,800/呎
+$28,830/呎
 (26年-07月-31日)</t>
         </is>
       </c>
@@ -31667,7 +31659,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -31677,7 +31669,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>43</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -31968,7 +31960,48 @@
 (26年-05月-11日)</t>
         </is>
       </c>
-      <c r="D11" s="20" t="inlineStr">
+      <c r="D11" s="22" t="inlineStr">
+        <is>
+          <t>C | 593呎 (2房)
+$1997万
+$33,671/呎
+(26年-08月-03日)</t>
+        </is>
+      </c>
+      <c r="E11" s="23" t="inlineStr">
+        <is>
+          <t>D | 992呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F11" s="21" t="inlineStr"/>
+      <c r="G11" s="21" t="inlineStr"/>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>A | 997呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>B | 597呎 (2房)
+$1959万
+$32,814/呎
+(26年-05月-29日)</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -31976,7 +32009,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E11" s="23" t="inlineStr">
+      <c r="E12" s="23" t="inlineStr">
         <is>
           <t>D | 992呎 (3房)
 -
@@ -31984,16 +32017,16 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F11" s="21" t="inlineStr"/>
-      <c r="G11" s="21" t="inlineStr"/>
-    </row>
-    <row r="12" ht="58" customHeight="1">
-      <c r="A12" s="19" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="B12" s="20" t="inlineStr">
+      <c r="F12" s="21" t="inlineStr"/>
+      <c r="G12" s="21" t="inlineStr"/>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
         <is>
           <t>A | 997呎 (3房)
 招标单位
@@ -32001,15 +32034,97 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C12" s="22" t="inlineStr">
+      <c r="C13" s="22" t="inlineStr">
         <is>
           <t>B | 597呎 (2房)
-$1959万
-$32,814/呎
-(26年-05月-29日)</t>
-        </is>
-      </c>
-      <c r="D12" s="20" t="inlineStr">
+$1967万
+$32,942/呎
+(26年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="inlineStr">
+        <is>
+          <t>C | 593呎 (2房)
+$1947万
+$32,832/呎
+(23年-12月-07日)</t>
+        </is>
+      </c>
+      <c r="E13" s="23" t="inlineStr">
+        <is>
+          <t>D | 992呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F13" s="21" t="inlineStr"/>
+      <c r="G13" s="21" t="inlineStr"/>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>A | 997呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>B | 597呎 (2房)
+$1898万
+$31,789/呎
+(26年-06月-05日)</t>
+        </is>
+      </c>
+      <c r="D14" s="22" t="inlineStr">
+        <is>
+          <t>C | 593呎 (2房)
+$1904万
+$32,106/呎
+(26年-07月-31日)</t>
+        </is>
+      </c>
+      <c r="E14" s="23" t="inlineStr">
+        <is>
+          <t>D | 992呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F14" s="21" t="inlineStr"/>
+      <c r="G14" s="21" t="inlineStr"/>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>A | 997呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>B | 597呎 (2房)
+$1928万
+$32,295/呎
+(26年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="D15" s="20" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -32017,7 +32132,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E12" s="23" t="inlineStr">
+      <c r="E15" s="23" t="inlineStr">
         <is>
           <t>D | 992呎 (3房)
 -
@@ -32025,40 +32140,40 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F12" s="21" t="inlineStr"/>
-      <c r="G12" s="21" t="inlineStr"/>
-    </row>
-    <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="19" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="B13" s="20" t="inlineStr">
+      <c r="F15" s="21" t="inlineStr"/>
+      <c r="G15" s="21" t="inlineStr"/>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
         <is>
           <t>A | 997呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C13" s="22" t="inlineStr">
+$3210万
+$32,201/呎
+(26年-05月-20日)</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
         <is>
           <t>B | 597呎 (2房)
-$1967万
-$32,942/呎
-(26年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="D13" s="22" t="inlineStr">
+$1883万
+$31,536/呎
+(26年-05月-06日)</t>
+        </is>
+      </c>
+      <c r="D16" s="25" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
-$1947万
-$32,832/呎
-(23年-12月-07日)</t>
-        </is>
-      </c>
-      <c r="E13" s="23" t="inlineStr">
+$2215万
+$37,352/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E16" s="23" t="inlineStr">
         <is>
           <t>D | 992呎 (3房)
 -
@@ -32066,40 +32181,40 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F13" s="21" t="inlineStr"/>
-      <c r="G13" s="21" t="inlineStr"/>
-    </row>
-    <row r="14" ht="58" customHeight="1">
-      <c r="A14" s="19" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="B14" s="20" t="inlineStr">
+      <c r="F16" s="21" t="inlineStr"/>
+      <c r="G16" s="21" t="inlineStr"/>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
         <is>
           <t>A | 997呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C14" s="22" t="inlineStr">
+$3170万
+$31,800/呎
+(26年-05月-18日)</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
         <is>
           <t>B | 597呎 (2房)
-$1898万
-$31,789/呎
-(26年-06月-05日)</t>
-        </is>
-      </c>
-      <c r="D14" s="22" t="inlineStr">
+$1871万
+$31,347/呎
+(26年-05月-05日)</t>
+        </is>
+      </c>
+      <c r="D17" s="25" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
-$1904万
-$32,106/呎
-(26年-07月-31日)</t>
-        </is>
-      </c>
-      <c r="E14" s="23" t="inlineStr">
+$2202万
+$37,130/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E17" s="23" t="inlineStr">
         <is>
           <t>D | 992呎 (3房)
 -
@@ -32107,32 +32222,32 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F14" s="21" t="inlineStr"/>
-      <c r="G14" s="21" t="inlineStr"/>
-    </row>
-    <row r="15" ht="58" customHeight="1">
-      <c r="A15" s="19" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="B15" s="20" t="inlineStr">
+      <c r="F17" s="21" t="inlineStr"/>
+      <c r="G17" s="21" t="inlineStr"/>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
         <is>
           <t>A | 997呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C15" s="22" t="inlineStr">
+$3121万
+$31,300/呎
+(26年-05月-26日)</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
         <is>
           <t>B | 597呎 (2房)
-$1928万
-$32,295/呎
-(26年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="D15" s="20" t="inlineStr">
+$1876万
+$31,419/呎
+(24年-04月-11日)</t>
+        </is>
+      </c>
+      <c r="D18" s="20" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -32140,7 +32255,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E15" s="23" t="inlineStr">
+      <c r="E18" s="23" t="inlineStr">
         <is>
           <t>D | 992呎 (3房)
 -
@@ -32148,40 +32263,40 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F15" s="21" t="inlineStr"/>
-      <c r="G15" s="21" t="inlineStr"/>
-    </row>
-    <row r="16" ht="58" customHeight="1">
-      <c r="A16" s="19" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="B16" s="22" t="inlineStr">
+      <c r="F18" s="21" t="inlineStr"/>
+      <c r="G18" s="21" t="inlineStr"/>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
         <is>
           <t>A | 997呎 (3房)
-$3210万
-$32,201/呎
-(26年-05月-20日)</t>
-        </is>
-      </c>
-      <c r="C16" s="22" t="inlineStr">
+$3071万
+$30,800/呎
+(26年-06月-05日)</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
         <is>
           <t>B | 597呎 (2房)
-$1883万
-$31,536/呎
+$1851万
+$31,005/呎
 (26年-05月-06日)</t>
         </is>
       </c>
-      <c r="D16" s="25" t="inlineStr">
+      <c r="D19" s="20" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
-$2215万
-$37,352/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E16" s="23" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E19" s="23" t="inlineStr">
         <is>
           <t>D | 992呎 (3房)
 -
@@ -32189,40 +32304,40 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F16" s="21" t="inlineStr"/>
-      <c r="G16" s="21" t="inlineStr"/>
-    </row>
-    <row r="17" ht="58" customHeight="1">
-      <c r="A17" s="19" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B17" s="22" t="inlineStr">
+      <c r="F19" s="21" t="inlineStr"/>
+      <c r="G19" s="21" t="inlineStr"/>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
         <is>
           <t>A | 997呎 (3房)
-$3170万
-$31,800/呎
-(26年-05月-18日)</t>
-        </is>
-      </c>
-      <c r="C17" s="22" t="inlineStr">
+$3021万
+$30,301/呎
+(26年-07月-28日)</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
         <is>
           <t>B | 597呎 (2房)
-$1871万
-$31,347/呎
-(26年-05月-05日)</t>
-        </is>
-      </c>
-      <c r="D17" s="25" t="inlineStr">
+$1923万
+$32,205/呎
+(23年-06月-12日)</t>
+        </is>
+      </c>
+      <c r="D20" s="22" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
-$2202万
-$37,130/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E17" s="23" t="inlineStr">
+$1907万
+$32,156/呎
+(23年-06月-12日)</t>
+        </is>
+      </c>
+      <c r="E20" s="23" t="inlineStr">
         <is>
           <t>D | 992呎 (3房)
 -
@@ -32230,40 +32345,40 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F17" s="21" t="inlineStr"/>
-      <c r="G17" s="21" t="inlineStr"/>
-    </row>
-    <row r="18" ht="58" customHeight="1">
-      <c r="A18" s="19" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="B18" s="22" t="inlineStr">
+      <c r="F20" s="21" t="inlineStr"/>
+      <c r="G20" s="21" t="inlineStr"/>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
         <is>
           <t>A | 997呎 (3房)
-$3121万
-$31,300/呎
-(26年-05月-26日)</t>
-        </is>
-      </c>
-      <c r="C18" s="22" t="inlineStr">
+$2971万
+$29,800/呎
+(26年-07月-20日)</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="inlineStr">
         <is>
           <t>B | 597呎 (2房)
-$1876万
-$31,419/呎
-(24年-04月-11日)</t>
-        </is>
-      </c>
-      <c r="D18" s="20" t="inlineStr">
+$1869万
+$31,310/呎
+(26年-08月-03日)</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="E18" s="23" t="inlineStr">
+$1833万
+$30,905/呎
+(23年-07月-04日)</t>
+        </is>
+      </c>
+      <c r="E21" s="23" t="inlineStr">
         <is>
           <t>D | 992呎 (3房)
 -
@@ -32271,129 +32386,6 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F18" s="21" t="inlineStr"/>
-      <c r="G18" s="21" t="inlineStr"/>
-    </row>
-    <row r="19" ht="58" customHeight="1">
-      <c r="A19" s="19" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B19" s="22" t="inlineStr">
-        <is>
-          <t>A | 997呎 (3房)
-$3071万
-$30,800/呎
-(26年-06月-05日)</t>
-        </is>
-      </c>
-      <c r="C19" s="22" t="inlineStr">
-        <is>
-          <t>B | 597呎 (2房)
-$1851万
-$31,005/呎
-(26年-05月-06日)</t>
-        </is>
-      </c>
-      <c r="D19" s="20" t="inlineStr">
-        <is>
-          <t>C | 593呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="E19" s="23" t="inlineStr">
-        <is>
-          <t>D | 992呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F19" s="21" t="inlineStr"/>
-      <c r="G19" s="21" t="inlineStr"/>
-    </row>
-    <row r="20" ht="58" customHeight="1">
-      <c r="A20" s="19" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B20" s="22" t="inlineStr">
-        <is>
-          <t>A | 997呎 (3房)
-$3021万
-$30,301/呎
-(26年-07月-28日)</t>
-        </is>
-      </c>
-      <c r="C20" s="22" t="inlineStr">
-        <is>
-          <t>B | 597呎 (2房)
-$1923万
-$32,205/呎
-(23年-06月-12日)</t>
-        </is>
-      </c>
-      <c r="D20" s="22" t="inlineStr">
-        <is>
-          <t>C | 593呎 (2房)
-$1907万
-$32,156/呎
-(23年-06月-12日)</t>
-        </is>
-      </c>
-      <c r="E20" s="23" t="inlineStr">
-        <is>
-          <t>D | 992呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F20" s="21" t="inlineStr"/>
-      <c r="G20" s="21" t="inlineStr"/>
-    </row>
-    <row r="21" ht="58" customHeight="1">
-      <c r="A21" s="19" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B21" s="22" t="inlineStr">
-        <is>
-          <t>A | 997呎 (3房)
-$2971万
-$29,800/呎
-(26年-07月-20日)</t>
-        </is>
-      </c>
-      <c r="C21" s="22" t="inlineStr">
-        <is>
-          <t>B | 597呎 (2房)
-$1869万
-$31,310/呎
-(26年-06月-30日)</t>
-        </is>
-      </c>
-      <c r="D21" s="22" t="inlineStr">
-        <is>
-          <t>C | 593呎 (2房)
-$1833万
-$30,905/呎
-(23年-07月-04日)</t>
-        </is>
-      </c>
-      <c r="E21" s="23" t="inlineStr">
-        <is>
-          <t>D | 992呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
       <c r="F21" s="21" t="inlineStr"/>
       <c r="G21" s="21" t="inlineStr"/>
     </row>
@@ -32408,7 +32400,7 @@
           <t>A | 997呎 (3房)
 $2921万
 $29,301/呎
-(26年-06月-26日)</t>
+(26年-08月-03日)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">

--- a/files/九龙-何文田-瑜一．天海.xlsx
+++ b/files/九龙-何文田-瑜一．天海.xlsx
@@ -20993,38 +20993,30 @@
       </c>
       <c r="F320" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G320" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H320" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I320" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="H320" s="5" t="n">
+        <v>17050000</v>
+      </c>
+      <c r="I320" s="5" t="n">
+        <v>31000</v>
       </c>
       <c r="J320" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K320" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L320" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K320" s="5" t="n">
+        <v>17050000</v>
+      </c>
+      <c r="L320" s="5" t="n">
+        <v>31000</v>
       </c>
       <c r="M320" s="3" t="inlineStr">
         <is>
@@ -21033,7 +21025,7 @@
       </c>
       <c r="N320" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -31659,7 +31651,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -31669,7 +31661,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>44</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -32698,12 +32690,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D29" s="20" t="inlineStr">
+      <c r="D29" s="22" t="inlineStr">
         <is>
           <t>C | 550呎 (2房)
-招标单位
--
-(在售)</t>
+$1705万
+$31,000/呎
+(26年-08月-14日)</t>
         </is>
       </c>
       <c r="E29" s="22" t="inlineStr">

--- a/files/九龙-何文田-瑜一．天海.xlsx
+++ b/files/九龙-何文田-瑜一．天海.xlsx
@@ -3043,38 +3043,30 @@
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H39" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I39" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="n">
+        <v>39840000</v>
+      </c>
+      <c r="I39" s="5" t="n">
+        <v>40000</v>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K39" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L39" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K39" s="5" t="n">
+        <v>39840000</v>
+      </c>
+      <c r="L39" s="5" t="n">
+        <v>40000</v>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
@@ -3083,7 +3075,7 @@
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -14645,7 +14637,7 @@
         </is>
       </c>
       <c r="E224" s="4" t="n">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="F224" s="3" t="inlineStr">
         <is>
@@ -14661,7 +14653,7 @@
         <v>8052700</v>
       </c>
       <c r="I224" s="5" t="n">
-        <v>25403</v>
+        <v>25483</v>
       </c>
       <c r="J224" s="3" t="inlineStr">
         <is>
@@ -14672,7 +14664,7 @@
         <v>8052700</v>
       </c>
       <c r="L224" s="5" t="n">
-        <v>25403</v>
+        <v>25483</v>
       </c>
       <c r="M224" s="3" t="inlineStr">
         <is>
@@ -15581,38 +15573,30 @@
       </c>
       <c r="F238" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H238" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I238" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="H238" s="5" t="n">
+        <v>36391000</v>
+      </c>
+      <c r="I238" s="5" t="n">
+        <v>36501</v>
       </c>
       <c r="J238" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K238" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L238" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K238" s="5" t="n">
+        <v>36391000</v>
+      </c>
+      <c r="L238" s="5" t="n">
+        <v>36501</v>
       </c>
       <c r="M238" s="3" t="inlineStr">
         <is>
@@ -15621,7 +15605,7 @@
       </c>
       <c r="N238" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -17054,7 +17038,7 @@
       </c>
       <c r="G260" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="H260" s="5" t="n">
@@ -29150,7 +29134,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -29160,7 +29144,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>81</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -29638,12 +29622,12 @@
 (25年-08月-07日)</t>
         </is>
       </c>
-      <c r="E15" s="20" t="inlineStr">
+      <c r="E15" s="22" t="inlineStr">
         <is>
           <t>D | 996呎 (3房)
-招标单位
--
-(在售)</t>
+$3984万
+$40,000/呎
+(26年-08月-19日)</t>
         </is>
       </c>
       <c r="F15" s="21" t="inlineStr"/>
@@ -31554,9 +31538,9 @@
       </c>
       <c r="D29" s="22" t="inlineStr">
         <is>
-          <t>C | 317呎 (1房)
+          <t>C | 316呎 (1房)
 $805万
-$25,403/呎
+$25,483/呎
 (24年-08月-29日)</t>
         </is>
       </c>
@@ -31651,7 +31635,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -31661,7 +31645,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>45</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -31813,7 +31797,48 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B8" s="20" t="inlineStr">
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>A | 997呎 (3房)
+$3639万
+$36,501/呎
+(26年-08月-21日)</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>B | 597呎 (2房)
+$2152万
+$36,046/呎
+(26年-06月-10日)</t>
+        </is>
+      </c>
+      <c r="D8" s="23" t="inlineStr">
+        <is>
+          <t>C | 593呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E8" s="23" t="inlineStr">
+        <is>
+          <t>D | 992呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F8" s="21" t="inlineStr"/>
+      <c r="G8" s="21" t="inlineStr"/>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>A | 997呎 (3房)
 招标单位
@@ -31821,15 +31846,15 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C8" s="22" t="inlineStr">
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t>B | 597呎 (2房)
-$2152万
-$36,046/呎
-(26年-06月-10日)</t>
-        </is>
-      </c>
-      <c r="D8" s="23" t="inlineStr">
+$2154万
+$36,089/呎
+(26年-05月-26日)</t>
+        </is>
+      </c>
+      <c r="D9" s="23" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 -
@@ -31837,7 +31862,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E8" s="23" t="inlineStr">
+      <c r="E9" s="23" t="inlineStr">
         <is>
           <t>D | 992呎 (3房)
 -
@@ -31845,16 +31870,16 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F8" s="21" t="inlineStr"/>
-      <c r="G8" s="21" t="inlineStr"/>
-    </row>
-    <row r="9" ht="58" customHeight="1">
-      <c r="A9" s="19" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B9" s="20" t="inlineStr">
+      <c r="F9" s="21" t="inlineStr"/>
+      <c r="G9" s="21" t="inlineStr"/>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>A | 997呎 (3房)
 招标单位
@@ -31862,23 +31887,23 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C9" s="22" t="inlineStr">
+      <c r="C10" s="22" t="inlineStr">
         <is>
           <t>B | 597呎 (2房)
-$2154万
-$36,089/呎
-(26年-05月-26日)</t>
-        </is>
-      </c>
-      <c r="D9" s="23" t="inlineStr">
+$2022万
+$33,871/呎
+(26年-05月-27日)</t>
+        </is>
+      </c>
+      <c r="D10" s="24" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E9" s="23" t="inlineStr">
+$2374万
+$40,039/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="E10" s="23" t="inlineStr">
         <is>
           <t>D | 992呎 (3房)
 -
@@ -31886,16 +31911,57 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F9" s="21" t="inlineStr"/>
-      <c r="G9" s="21" t="inlineStr"/>
-    </row>
-    <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="19" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="B10" s="20" t="inlineStr">
+      <c r="F10" s="21" t="inlineStr"/>
+      <c r="G10" s="21" t="inlineStr"/>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>A | 997呎 (3房)
+$3420万
+$34,301/呎
+(26年-06月-03日)</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>B | 597呎 (2房)
+$1990万
+$33,337/呎
+(26年-05月-11日)</t>
+        </is>
+      </c>
+      <c r="D11" s="22" t="inlineStr">
+        <is>
+          <t>C | 593呎 (2房)
+$1997万
+$33,671/呎
+(26年-08月-03日)</t>
+        </is>
+      </c>
+      <c r="E11" s="23" t="inlineStr">
+        <is>
+          <t>D | 992呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F11" s="21" t="inlineStr"/>
+      <c r="G11" s="21" t="inlineStr"/>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
         <is>
           <t>A | 997呎 (3房)
 招标单位
@@ -31903,23 +31969,23 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C10" s="22" t="inlineStr">
+      <c r="C12" s="22" t="inlineStr">
         <is>
           <t>B | 597呎 (2房)
-$2022万
-$33,871/呎
-(26年-05月-27日)</t>
-        </is>
-      </c>
-      <c r="D10" s="24" t="inlineStr">
+$1959万
+$32,814/呎
+(26年-05月-29日)</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
-$2374万
-$40,039/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="E10" s="23" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E12" s="23" t="inlineStr">
         <is>
           <t>D | 992呎 (3房)
 -
@@ -31927,40 +31993,40 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F10" s="21" t="inlineStr"/>
-      <c r="G10" s="21" t="inlineStr"/>
-    </row>
-    <row r="11" ht="58" customHeight="1">
-      <c r="A11" s="19" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="B11" s="22" t="inlineStr">
+      <c r="F12" s="21" t="inlineStr"/>
+      <c r="G12" s="21" t="inlineStr"/>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
         <is>
           <t>A | 997呎 (3房)
-$3420万
-$34,301/呎
-(26年-06月-03日)</t>
-        </is>
-      </c>
-      <c r="C11" s="22" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
         <is>
           <t>B | 597呎 (2房)
-$1990万
-$33,337/呎
-(26年-05月-11日)</t>
-        </is>
-      </c>
-      <c r="D11" s="22" t="inlineStr">
+$1967万
+$32,942/呎
+(26年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
-$1997万
-$33,671/呎
-(26年-08月-03日)</t>
-        </is>
-      </c>
-      <c r="E11" s="23" t="inlineStr">
+$1947万
+$32,832/呎
+(23年-12月-07日)</t>
+        </is>
+      </c>
+      <c r="E13" s="23" t="inlineStr">
         <is>
           <t>D | 992呎 (3房)
 -
@@ -31968,16 +32034,16 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F11" s="21" t="inlineStr"/>
-      <c r="G11" s="21" t="inlineStr"/>
-    </row>
-    <row r="12" ht="58" customHeight="1">
-      <c r="A12" s="19" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="B12" s="20" t="inlineStr">
+      <c r="F13" s="21" t="inlineStr"/>
+      <c r="G13" s="21" t="inlineStr"/>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
         <is>
           <t>A | 997呎 (3房)
 招标单位
@@ -31985,88 +32051,6 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C12" s="22" t="inlineStr">
-        <is>
-          <t>B | 597呎 (2房)
-$1959万
-$32,814/呎
-(26年-05月-29日)</t>
-        </is>
-      </c>
-      <c r="D12" s="20" t="inlineStr">
-        <is>
-          <t>C | 593呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="E12" s="23" t="inlineStr">
-        <is>
-          <t>D | 992呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F12" s="21" t="inlineStr"/>
-      <c r="G12" s="21" t="inlineStr"/>
-    </row>
-    <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="19" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="B13" s="20" t="inlineStr">
-        <is>
-          <t>A | 997呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C13" s="22" t="inlineStr">
-        <is>
-          <t>B | 597呎 (2房)
-$1967万
-$32,942/呎
-(26年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="D13" s="22" t="inlineStr">
-        <is>
-          <t>C | 593呎 (2房)
-$1947万
-$32,832/呎
-(23年-12月-07日)</t>
-        </is>
-      </c>
-      <c r="E13" s="23" t="inlineStr">
-        <is>
-          <t>D | 992呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F13" s="21" t="inlineStr"/>
-      <c r="G13" s="21" t="inlineStr"/>
-    </row>
-    <row r="14" ht="58" customHeight="1">
-      <c r="A14" s="19" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="B14" s="20" t="inlineStr">
-        <is>
-          <t>A | 997呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
       <c r="C14" s="22" t="inlineStr">
         <is>
           <t>B | 597呎 (2房)
@@ -32080,7 +32064,7 @@
           <t>C | 593呎 (2房)
 $1904万
 $32,106/呎
-(26年-07月-31日)</t>
+(26年-08月-20日)</t>
         </is>
       </c>
       <c r="E14" s="23" t="inlineStr">

--- a/files/九龙-何文田-瑜一．天海.xlsx
+++ b/files/九龙-何文田-瑜一．天海.xlsx
@@ -10120,7 +10120,7 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="H151" s="5" t="n">
@@ -21246,7 +21246,7 @@
       </c>
       <c r="G324" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="H324" s="5" t="n">
@@ -22187,38 +22187,30 @@
       </c>
       <c r="F339" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G339" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H339" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I339" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="H339" s="5" t="n">
+        <v>31150400</v>
+      </c>
+      <c r="I339" s="5" t="n">
+        <v>32550</v>
       </c>
       <c r="J339" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K339" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L339" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K339" s="5" t="n">
+        <v>31150400</v>
+      </c>
+      <c r="L339" s="5" t="n">
+        <v>32550</v>
       </c>
       <c r="M339" s="3" t="inlineStr">
         <is>
@@ -22227,7 +22219,7 @@
       </c>
       <c r="N339" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -30820,7 +30812,7 @@
           <t>A | 959呎 (3房)
 $2765万
 $28,830/呎
-(26年-07月-31日)</t>
+(26年-08月-25日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -32708,7 +32700,7 @@
           <t>MAISON D | 889呎 (3房)
 $3201万
 $36,007/呎
-(26年-07月-31日)</t>
+(26年-08月-25日)</t>
         </is>
       </c>
       <c r="G30" s="22" t="inlineStr">
@@ -32793,7 +32785,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -32803,7 +32795,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>122</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -32949,12 +32941,12 @@
           <t>27</t>
         </is>
       </c>
-      <c r="B7" s="20" t="inlineStr">
+      <c r="B7" s="22" t="inlineStr">
         <is>
           <t>A | 957呎 (3房)
-招标单位
--
-(在售)</t>
+$3115万
+$32,550/呎
+(26年-08月-24日)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
